--- a/src/data/Sources_and_Definitions.xlsx
+++ b/src/data/Sources_and_Definitions.xlsx
@@ -1127,10 +1127,10 @@
     <t>The count of children in kinship or relative care (excluding masked values)</t>
   </si>
   <si>
-    <t>The number of certified foster homes on 9/30/2023, including licensed and relative care</t>
-  </si>
-  <si>
-    <t>The number of children served in-home on 9/30/2023</t>
+    <t>The total number of certified foster homes on 9/30/2024</t>
+  </si>
+  <si>
+    <t>The total number of in-home cases on 9/30/2024</t>
   </si>
   <si>
     <t>Pennsylvania</t>
@@ -1549,7 +1549,7 @@
     </font>
     <font>
       <b/>
-      <sz val="8.0"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1561,12 +1561,19 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="8.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1606,11 +1613,6 @@
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -1708,7 +1710,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1739,72 +1741,79 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -2061,1646 +2070,4509 @@
       <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>44619.0</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="N2" s="9"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="N2" s="10"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9" t="s">
+      <c r="H4" s="10"/>
+      <c r="I4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="9"/>
+      <c r="L4" s="10"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="10" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="14">
         <v>45658.0</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="10" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="14">
         <v>45807.0</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <v>45784.0</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="18" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="14">
         <v>45504.0</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="K10" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="N10" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="K11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="N11" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <v>45659.0</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N12" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="N13" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="O13" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="K14" s="9"/>
-      <c r="N14" s="9"/>
+      <c r="K14" s="10"/>
+      <c r="N14" s="10"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="K15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="N15" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="K16" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="L16" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="N16" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="O16" s="9" t="s">
+      <c r="O16" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="14">
         <v>45757.0</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9" t="s">
+      <c r="E17" s="10"/>
+      <c r="F17" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="K17" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N17" s="9" t="s">
+      <c r="N17" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="O17" s="9" t="s">
+      <c r="O17" s="10" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="K18" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N18" s="9" t="s">
+      <c r="N18" s="10" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="24">
         <v>45655.0</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="G19" s="24" t="s">
+      <c r="G19" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="K19" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N19" s="9" t="s">
+      <c r="N19" s="10" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="14">
         <v>45769.0</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K20" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="9" t="s">
+      <c r="N20" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="14">
         <v>45658.0</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="10" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="K22" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="N22" s="10" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="K23" s="9" t="s">
+      <c r="K23" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N23" s="9" t="s">
+      <c r="N23" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="O23" s="9" t="s">
+      <c r="O23" s="10" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="26" t="s">
+      <c r="H24" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="J24" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="K24" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N24" s="9" t="s">
+      <c r="N24" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="10" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="14">
         <v>45770.0</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="L26" s="10" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="28">
         <v>2024.0</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="J27" s="9" t="s">
+      <c r="J27" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="K27" s="9" t="s">
+      <c r="K27" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="L27" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="N27" s="9" t="s">
+      <c r="N27" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="B28" s="29"/>
+      <c r="C28" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="D28" s="17"/>
+      <c r="D28" s="18"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="F29" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="K29" s="9" t="s">
+      <c r="K29" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="9" t="s">
+      <c r="N29" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="31">
         <v>45657.0</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="E30" s="29" t="s">
+      <c r="E30" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="F30" s="29" t="s">
+      <c r="F30" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="G30" s="27" t="s">
+      <c r="G30" s="30" t="s">
         <v>223</v>
       </c>
-      <c r="H30" s="30"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="27"/>
-      <c r="O30" s="30"/>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="30"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="30"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="33"/>
+      <c r="S30" s="33"/>
+      <c r="T30" s="33"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="I31" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="K31" s="9" t="s">
+      <c r="K31" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="L31" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="N31" s="9" t="s">
+      <c r="N31" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="K32" s="9" t="s">
+      <c r="K32" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="9" t="s">
+      <c r="N32" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="E33" s="31" t="s">
+      <c r="E33" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="I33" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="J33" s="9" t="s">
+      <c r="J33" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="K33" s="9" t="s">
+      <c r="K33" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N33" s="9" t="s">
+      <c r="N33" s="10" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="14">
         <v>45763.0</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="D34" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="E34" s="32" t="s">
+      <c r="E34" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="I34" s="9" t="s">
+      <c r="I34" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="J34" s="9" t="s">
+      <c r="J34" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="K34" s="9" t="s">
+      <c r="K34" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="N34" s="9" t="s">
+      <c r="N34" s="10" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="14">
         <v>45658.0</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="E35" s="32" t="s">
+      <c r="E35" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="9" t="s">
+      <c r="K35" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N35" s="9" t="s">
+      <c r="N35" s="10" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="E36" s="32" t="s">
+      <c r="E36" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="I36" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="J36" s="10" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="14">
         <v>45658.0</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="J37" s="9" t="s">
+      <c r="J37" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="K37" s="9" t="s">
+      <c r="K37" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N37" s="9" t="s">
+      <c r="N37" s="10" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="H38" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="I38" s="9" t="s">
+      <c r="I38" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="K38" s="9" t="s">
+      <c r="K38" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="L38" s="9" t="s">
+      <c r="L38" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="N38" s="9" t="s">
+      <c r="N38" s="10" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="9" t="s">
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B39" s="13">
-        <v>45199.0</v>
-      </c>
-      <c r="C39" s="9" t="s">
+      <c r="B39" s="14">
+        <v>45657.0</v>
+      </c>
+      <c r="C39" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="I39" s="9" t="s">
+      <c r="I39" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="L39" s="9" t="s">
+      <c r="L39" s="10" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="14">
         <v>44834.0</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="J40" s="9" t="s">
+      <c r="J40" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="K40" s="9" t="s">
+      <c r="K40" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="N40" s="9" t="s">
+      <c r="N40" s="10" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="14">
         <v>45748.0</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H41" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="I41" s="9" t="s">
+      <c r="I41" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="J41" s="9" t="s">
+      <c r="J41" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="K41" s="9" t="s">
+      <c r="K41" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="L41" s="9" t="s">
+      <c r="L41" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="N41" s="9" t="s">
+      <c r="N41" s="10" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="14">
         <v>45803.0</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="F42" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H42" s="9" t="s">
+      <c r="H42" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="I42" s="9" t="s">
+      <c r="I42" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="J42" s="9" t="s">
+      <c r="J42" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="K42" s="9" t="s">
+      <c r="K42" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="L42" s="9" t="s">
+      <c r="L42" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="N42" s="9" t="s">
+      <c r="N42" s="10" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="14">
         <v>45473.0</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="D43" s="22" t="s">
         <v>322</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9" t="s">
+      <c r="F43" s="10"/>
+      <c r="G43" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="I43" s="9" t="s">
+      <c r="I43" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="J43" s="9" t="s">
+      <c r="J43" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="K43" s="9" t="s">
+      <c r="K43" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="L43" s="9" t="s">
+      <c r="L43" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="N43" s="9" t="s">
+      <c r="N43" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="O43" s="9" t="s">
+      <c r="O43" s="10" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F44" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I44" s="9" t="s">
+      <c r="I44" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="J44" s="9" t="s">
+      <c r="J44" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="O44" s="9"/>
+      <c r="O44" s="10"/>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="14">
         <v>45535.0</v>
       </c>
-      <c r="C45" s="33" t="s">
+      <c r="C45" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G45" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="I45" s="9" t="s">
+      <c r="I45" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="J45" s="9" t="s">
+      <c r="J45" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="K45" s="9" t="s">
+      <c r="K45" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="9" t="s">
+      <c r="L45" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="N45" s="9" t="s">
+      <c r="N45" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="O45" s="9"/>
+      <c r="O45" s="10"/>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="D46" s="17"/>
+      <c r="D46" s="18"/>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="s">
+      <c r="A47" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="14">
         <v>45565.0</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="I47" s="9" t="s">
+      <c r="I47" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="J47" s="9" t="s">
+      <c r="J47" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="K47" s="9" t="s">
+      <c r="K47" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="L47" s="9" t="s">
+      <c r="L47" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="N47" s="9" t="s">
+      <c r="N47" s="10" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="14">
         <v>45658.0</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="E48" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="F48" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="G48" s="9" t="s">
+      <c r="G48" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="J48" s="9" t="s">
+      <c r="J48" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="K48" s="9" t="s">
+      <c r="K48" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="N48" s="9" t="s">
+      <c r="N48" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="O48" s="9" t="s">
+      <c r="O48" s="10" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="14">
         <v>45473.0</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="E49" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G49" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="I49" s="9" t="s">
+      <c r="I49" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="K49" s="9" t="s">
+      <c r="K49" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="N49" s="9" t="s">
+      <c r="N49" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="27" t="s">
+      <c r="A50" s="30" t="s">
         <v>375</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="F50" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="I50" s="10" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="14">
         <v>45291.0</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="10" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="14">
         <v>45657.0</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G52" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="I52" s="9" t="s">
+      <c r="I52" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="J52" s="9" t="s">
+      <c r="J52" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="K52" s="9" t="s">
+      <c r="K52" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="N52" s="9" t="s">
+      <c r="N52" s="10" t="s">
         <v>395</v>
       </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="29"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="29"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="29"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="29"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="29"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="29"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="29"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="29"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="29"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="29"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="29"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="29"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="29"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="29"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="29"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="29"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="29"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="29"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="29"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="29"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="29"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="29"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="29"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="29"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="29"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="29"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="29"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="29"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="29"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="29"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="29"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="29"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="29"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="29"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="29"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="29"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="29"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="29"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="29"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="29"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="29"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="29"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="29"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="29"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="29"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="29"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="29"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="29"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="29"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="29"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="29"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="29"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="29"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="29"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="29"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="29"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="29"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="29"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="29"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="29"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="29"/>
+    </row>
+    <row r="114">
+      <c r="B114" s="29"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="29"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="29"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="29"/>
+    </row>
+    <row r="118">
+      <c r="B118" s="29"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="29"/>
+    </row>
+    <row r="120">
+      <c r="B120" s="29"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="29"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="29"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="29"/>
+    </row>
+    <row r="124">
+      <c r="B124" s="29"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="29"/>
+    </row>
+    <row r="126">
+      <c r="B126" s="29"/>
+    </row>
+    <row r="127">
+      <c r="B127" s="29"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="29"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="29"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="29"/>
+    </row>
+    <row r="131">
+      <c r="B131" s="29"/>
+    </row>
+    <row r="132">
+      <c r="B132" s="29"/>
+    </row>
+    <row r="133">
+      <c r="B133" s="29"/>
+    </row>
+    <row r="134">
+      <c r="B134" s="29"/>
+    </row>
+    <row r="135">
+      <c r="B135" s="29"/>
+    </row>
+    <row r="136">
+      <c r="B136" s="29"/>
+    </row>
+    <row r="137">
+      <c r="B137" s="29"/>
+    </row>
+    <row r="138">
+      <c r="B138" s="29"/>
+    </row>
+    <row r="139">
+      <c r="B139" s="29"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="29"/>
+    </row>
+    <row r="141">
+      <c r="B141" s="29"/>
+    </row>
+    <row r="142">
+      <c r="B142" s="29"/>
+    </row>
+    <row r="143">
+      <c r="B143" s="29"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="29"/>
+    </row>
+    <row r="145">
+      <c r="B145" s="29"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="29"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="29"/>
+    </row>
+    <row r="148">
+      <c r="B148" s="29"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="29"/>
+    </row>
+    <row r="150">
+      <c r="B150" s="29"/>
+    </row>
+    <row r="151">
+      <c r="B151" s="29"/>
+    </row>
+    <row r="152">
+      <c r="B152" s="29"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="29"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="29"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="29"/>
+    </row>
+    <row r="156">
+      <c r="B156" s="29"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="29"/>
+    </row>
+    <row r="158">
+      <c r="B158" s="29"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="29"/>
+    </row>
+    <row r="160">
+      <c r="B160" s="29"/>
+    </row>
+    <row r="161">
+      <c r="B161" s="29"/>
+    </row>
+    <row r="162">
+      <c r="B162" s="29"/>
+    </row>
+    <row r="163">
+      <c r="B163" s="29"/>
+    </row>
+    <row r="164">
+      <c r="B164" s="29"/>
+    </row>
+    <row r="165">
+      <c r="B165" s="29"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="29"/>
+    </row>
+    <row r="167">
+      <c r="B167" s="29"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="29"/>
+    </row>
+    <row r="169">
+      <c r="B169" s="29"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="29"/>
+    </row>
+    <row r="171">
+      <c r="B171" s="29"/>
+    </row>
+    <row r="172">
+      <c r="B172" s="29"/>
+    </row>
+    <row r="173">
+      <c r="B173" s="29"/>
+    </row>
+    <row r="174">
+      <c r="B174" s="29"/>
+    </row>
+    <row r="175">
+      <c r="B175" s="29"/>
+    </row>
+    <row r="176">
+      <c r="B176" s="29"/>
+    </row>
+    <row r="177">
+      <c r="B177" s="29"/>
+    </row>
+    <row r="178">
+      <c r="B178" s="29"/>
+    </row>
+    <row r="179">
+      <c r="B179" s="29"/>
+    </row>
+    <row r="180">
+      <c r="B180" s="29"/>
+    </row>
+    <row r="181">
+      <c r="B181" s="29"/>
+    </row>
+    <row r="182">
+      <c r="B182" s="29"/>
+    </row>
+    <row r="183">
+      <c r="B183" s="29"/>
+    </row>
+    <row r="184">
+      <c r="B184" s="29"/>
+    </row>
+    <row r="185">
+      <c r="B185" s="29"/>
+    </row>
+    <row r="186">
+      <c r="B186" s="29"/>
+    </row>
+    <row r="187">
+      <c r="B187" s="29"/>
+    </row>
+    <row r="188">
+      <c r="B188" s="29"/>
+    </row>
+    <row r="189">
+      <c r="B189" s="29"/>
+    </row>
+    <row r="190">
+      <c r="B190" s="29"/>
+    </row>
+    <row r="191">
+      <c r="B191" s="29"/>
+    </row>
+    <row r="192">
+      <c r="B192" s="29"/>
+    </row>
+    <row r="193">
+      <c r="B193" s="29"/>
+    </row>
+    <row r="194">
+      <c r="B194" s="29"/>
+    </row>
+    <row r="195">
+      <c r="B195" s="29"/>
+    </row>
+    <row r="196">
+      <c r="B196" s="29"/>
+    </row>
+    <row r="197">
+      <c r="B197" s="29"/>
+    </row>
+    <row r="198">
+      <c r="B198" s="29"/>
+    </row>
+    <row r="199">
+      <c r="B199" s="29"/>
+    </row>
+    <row r="200">
+      <c r="B200" s="29"/>
+    </row>
+    <row r="201">
+      <c r="B201" s="29"/>
+    </row>
+    <row r="202">
+      <c r="B202" s="29"/>
+    </row>
+    <row r="203">
+      <c r="B203" s="29"/>
+    </row>
+    <row r="204">
+      <c r="B204" s="29"/>
+    </row>
+    <row r="205">
+      <c r="B205" s="29"/>
+    </row>
+    <row r="206">
+      <c r="B206" s="29"/>
+    </row>
+    <row r="207">
+      <c r="B207" s="29"/>
+    </row>
+    <row r="208">
+      <c r="B208" s="29"/>
+    </row>
+    <row r="209">
+      <c r="B209" s="29"/>
+    </row>
+    <row r="210">
+      <c r="B210" s="29"/>
+    </row>
+    <row r="211">
+      <c r="B211" s="29"/>
+    </row>
+    <row r="212">
+      <c r="B212" s="29"/>
+    </row>
+    <row r="213">
+      <c r="B213" s="29"/>
+    </row>
+    <row r="214">
+      <c r="B214" s="29"/>
+    </row>
+    <row r="215">
+      <c r="B215" s="29"/>
+    </row>
+    <row r="216">
+      <c r="B216" s="29"/>
+    </row>
+    <row r="217">
+      <c r="B217" s="29"/>
+    </row>
+    <row r="218">
+      <c r="B218" s="29"/>
+    </row>
+    <row r="219">
+      <c r="B219" s="29"/>
+    </row>
+    <row r="220">
+      <c r="B220" s="29"/>
+    </row>
+    <row r="221">
+      <c r="B221" s="29"/>
+    </row>
+    <row r="222">
+      <c r="B222" s="29"/>
+    </row>
+    <row r="223">
+      <c r="B223" s="29"/>
+    </row>
+    <row r="224">
+      <c r="B224" s="29"/>
+    </row>
+    <row r="225">
+      <c r="B225" s="29"/>
+    </row>
+    <row r="226">
+      <c r="B226" s="29"/>
+    </row>
+    <row r="227">
+      <c r="B227" s="29"/>
+    </row>
+    <row r="228">
+      <c r="B228" s="29"/>
+    </row>
+    <row r="229">
+      <c r="B229" s="29"/>
+    </row>
+    <row r="230">
+      <c r="B230" s="29"/>
+    </row>
+    <row r="231">
+      <c r="B231" s="29"/>
+    </row>
+    <row r="232">
+      <c r="B232" s="29"/>
+    </row>
+    <row r="233">
+      <c r="B233" s="29"/>
+    </row>
+    <row r="234">
+      <c r="B234" s="29"/>
+    </row>
+    <row r="235">
+      <c r="B235" s="29"/>
+    </row>
+    <row r="236">
+      <c r="B236" s="29"/>
+    </row>
+    <row r="237">
+      <c r="B237" s="29"/>
+    </row>
+    <row r="238">
+      <c r="B238" s="29"/>
+    </row>
+    <row r="239">
+      <c r="B239" s="29"/>
+    </row>
+    <row r="240">
+      <c r="B240" s="29"/>
+    </row>
+    <row r="241">
+      <c r="B241" s="29"/>
+    </row>
+    <row r="242">
+      <c r="B242" s="29"/>
+    </row>
+    <row r="243">
+      <c r="B243" s="29"/>
+    </row>
+    <row r="244">
+      <c r="B244" s="29"/>
+    </row>
+    <row r="245">
+      <c r="B245" s="29"/>
+    </row>
+    <row r="246">
+      <c r="B246" s="29"/>
+    </row>
+    <row r="247">
+      <c r="B247" s="29"/>
+    </row>
+    <row r="248">
+      <c r="B248" s="29"/>
+    </row>
+    <row r="249">
+      <c r="B249" s="29"/>
+    </row>
+    <row r="250">
+      <c r="B250" s="29"/>
+    </row>
+    <row r="251">
+      <c r="B251" s="29"/>
+    </row>
+    <row r="252">
+      <c r="B252" s="29"/>
+    </row>
+    <row r="253">
+      <c r="B253" s="29"/>
+    </row>
+    <row r="254">
+      <c r="B254" s="29"/>
+    </row>
+    <row r="255">
+      <c r="B255" s="29"/>
+    </row>
+    <row r="256">
+      <c r="B256" s="29"/>
+    </row>
+    <row r="257">
+      <c r="B257" s="29"/>
+    </row>
+    <row r="258">
+      <c r="B258" s="29"/>
+    </row>
+    <row r="259">
+      <c r="B259" s="29"/>
+    </row>
+    <row r="260">
+      <c r="B260" s="29"/>
+    </row>
+    <row r="261">
+      <c r="B261" s="29"/>
+    </row>
+    <row r="262">
+      <c r="B262" s="29"/>
+    </row>
+    <row r="263">
+      <c r="B263" s="29"/>
+    </row>
+    <row r="264">
+      <c r="B264" s="29"/>
+    </row>
+    <row r="265">
+      <c r="B265" s="29"/>
+    </row>
+    <row r="266">
+      <c r="B266" s="29"/>
+    </row>
+    <row r="267">
+      <c r="B267" s="29"/>
+    </row>
+    <row r="268">
+      <c r="B268" s="29"/>
+    </row>
+    <row r="269">
+      <c r="B269" s="29"/>
+    </row>
+    <row r="270">
+      <c r="B270" s="29"/>
+    </row>
+    <row r="271">
+      <c r="B271" s="29"/>
+    </row>
+    <row r="272">
+      <c r="B272" s="29"/>
+    </row>
+    <row r="273">
+      <c r="B273" s="29"/>
+    </row>
+    <row r="274">
+      <c r="B274" s="29"/>
+    </row>
+    <row r="275">
+      <c r="B275" s="29"/>
+    </row>
+    <row r="276">
+      <c r="B276" s="29"/>
+    </row>
+    <row r="277">
+      <c r="B277" s="29"/>
+    </row>
+    <row r="278">
+      <c r="B278" s="29"/>
+    </row>
+    <row r="279">
+      <c r="B279" s="29"/>
+    </row>
+    <row r="280">
+      <c r="B280" s="29"/>
+    </row>
+    <row r="281">
+      <c r="B281" s="29"/>
+    </row>
+    <row r="282">
+      <c r="B282" s="29"/>
+    </row>
+    <row r="283">
+      <c r="B283" s="29"/>
+    </row>
+    <row r="284">
+      <c r="B284" s="29"/>
+    </row>
+    <row r="285">
+      <c r="B285" s="29"/>
+    </row>
+    <row r="286">
+      <c r="B286" s="29"/>
+    </row>
+    <row r="287">
+      <c r="B287" s="29"/>
+    </row>
+    <row r="288">
+      <c r="B288" s="29"/>
+    </row>
+    <row r="289">
+      <c r="B289" s="29"/>
+    </row>
+    <row r="290">
+      <c r="B290" s="29"/>
+    </row>
+    <row r="291">
+      <c r="B291" s="29"/>
+    </row>
+    <row r="292">
+      <c r="B292" s="29"/>
+    </row>
+    <row r="293">
+      <c r="B293" s="29"/>
+    </row>
+    <row r="294">
+      <c r="B294" s="29"/>
+    </row>
+    <row r="295">
+      <c r="B295" s="29"/>
+    </row>
+    <row r="296">
+      <c r="B296" s="29"/>
+    </row>
+    <row r="297">
+      <c r="B297" s="29"/>
+    </row>
+    <row r="298">
+      <c r="B298" s="29"/>
+    </row>
+    <row r="299">
+      <c r="B299" s="29"/>
+    </row>
+    <row r="300">
+      <c r="B300" s="29"/>
+    </row>
+    <row r="301">
+      <c r="B301" s="29"/>
+    </row>
+    <row r="302">
+      <c r="B302" s="29"/>
+    </row>
+    <row r="303">
+      <c r="B303" s="29"/>
+    </row>
+    <row r="304">
+      <c r="B304" s="29"/>
+    </row>
+    <row r="305">
+      <c r="B305" s="29"/>
+    </row>
+    <row r="306">
+      <c r="B306" s="29"/>
+    </row>
+    <row r="307">
+      <c r="B307" s="29"/>
+    </row>
+    <row r="308">
+      <c r="B308" s="29"/>
+    </row>
+    <row r="309">
+      <c r="B309" s="29"/>
+    </row>
+    <row r="310">
+      <c r="B310" s="29"/>
+    </row>
+    <row r="311">
+      <c r="B311" s="29"/>
+    </row>
+    <row r="312">
+      <c r="B312" s="29"/>
+    </row>
+    <row r="313">
+      <c r="B313" s="29"/>
+    </row>
+    <row r="314">
+      <c r="B314" s="29"/>
+    </row>
+    <row r="315">
+      <c r="B315" s="29"/>
+    </row>
+    <row r="316">
+      <c r="B316" s="29"/>
+    </row>
+    <row r="317">
+      <c r="B317" s="29"/>
+    </row>
+    <row r="318">
+      <c r="B318" s="29"/>
+    </row>
+    <row r="319">
+      <c r="B319" s="29"/>
+    </row>
+    <row r="320">
+      <c r="B320" s="29"/>
+    </row>
+    <row r="321">
+      <c r="B321" s="29"/>
+    </row>
+    <row r="322">
+      <c r="B322" s="29"/>
+    </row>
+    <row r="323">
+      <c r="B323" s="29"/>
+    </row>
+    <row r="324">
+      <c r="B324" s="29"/>
+    </row>
+    <row r="325">
+      <c r="B325" s="29"/>
+    </row>
+    <row r="326">
+      <c r="B326" s="29"/>
+    </row>
+    <row r="327">
+      <c r="B327" s="29"/>
+    </row>
+    <row r="328">
+      <c r="B328" s="29"/>
+    </row>
+    <row r="329">
+      <c r="B329" s="29"/>
+    </row>
+    <row r="330">
+      <c r="B330" s="29"/>
+    </row>
+    <row r="331">
+      <c r="B331" s="29"/>
+    </row>
+    <row r="332">
+      <c r="B332" s="29"/>
+    </row>
+    <row r="333">
+      <c r="B333" s="29"/>
+    </row>
+    <row r="334">
+      <c r="B334" s="29"/>
+    </row>
+    <row r="335">
+      <c r="B335" s="29"/>
+    </row>
+    <row r="336">
+      <c r="B336" s="29"/>
+    </row>
+    <row r="337">
+      <c r="B337" s="29"/>
+    </row>
+    <row r="338">
+      <c r="B338" s="29"/>
+    </row>
+    <row r="339">
+      <c r="B339" s="29"/>
+    </row>
+    <row r="340">
+      <c r="B340" s="29"/>
+    </row>
+    <row r="341">
+      <c r="B341" s="29"/>
+    </row>
+    <row r="342">
+      <c r="B342" s="29"/>
+    </row>
+    <row r="343">
+      <c r="B343" s="29"/>
+    </row>
+    <row r="344">
+      <c r="B344" s="29"/>
+    </row>
+    <row r="345">
+      <c r="B345" s="29"/>
+    </row>
+    <row r="346">
+      <c r="B346" s="29"/>
+    </row>
+    <row r="347">
+      <c r="B347" s="29"/>
+    </row>
+    <row r="348">
+      <c r="B348" s="29"/>
+    </row>
+    <row r="349">
+      <c r="B349" s="29"/>
+    </row>
+    <row r="350">
+      <c r="B350" s="29"/>
+    </row>
+    <row r="351">
+      <c r="B351" s="29"/>
+    </row>
+    <row r="352">
+      <c r="B352" s="29"/>
+    </row>
+    <row r="353">
+      <c r="B353" s="29"/>
+    </row>
+    <row r="354">
+      <c r="B354" s="29"/>
+    </row>
+    <row r="355">
+      <c r="B355" s="29"/>
+    </row>
+    <row r="356">
+      <c r="B356" s="29"/>
+    </row>
+    <row r="357">
+      <c r="B357" s="29"/>
+    </row>
+    <row r="358">
+      <c r="B358" s="29"/>
+    </row>
+    <row r="359">
+      <c r="B359" s="29"/>
+    </row>
+    <row r="360">
+      <c r="B360" s="29"/>
+    </row>
+    <row r="361">
+      <c r="B361" s="29"/>
+    </row>
+    <row r="362">
+      <c r="B362" s="29"/>
+    </row>
+    <row r="363">
+      <c r="B363" s="29"/>
+    </row>
+    <row r="364">
+      <c r="B364" s="29"/>
+    </row>
+    <row r="365">
+      <c r="B365" s="29"/>
+    </row>
+    <row r="366">
+      <c r="B366" s="29"/>
+    </row>
+    <row r="367">
+      <c r="B367" s="29"/>
+    </row>
+    <row r="368">
+      <c r="B368" s="29"/>
+    </row>
+    <row r="369">
+      <c r="B369" s="29"/>
+    </row>
+    <row r="370">
+      <c r="B370" s="29"/>
+    </row>
+    <row r="371">
+      <c r="B371" s="29"/>
+    </row>
+    <row r="372">
+      <c r="B372" s="29"/>
+    </row>
+    <row r="373">
+      <c r="B373" s="29"/>
+    </row>
+    <row r="374">
+      <c r="B374" s="29"/>
+    </row>
+    <row r="375">
+      <c r="B375" s="29"/>
+    </row>
+    <row r="376">
+      <c r="B376" s="29"/>
+    </row>
+    <row r="377">
+      <c r="B377" s="29"/>
+    </row>
+    <row r="378">
+      <c r="B378" s="29"/>
+    </row>
+    <row r="379">
+      <c r="B379" s="29"/>
+    </row>
+    <row r="380">
+      <c r="B380" s="29"/>
+    </row>
+    <row r="381">
+      <c r="B381" s="29"/>
+    </row>
+    <row r="382">
+      <c r="B382" s="29"/>
+    </row>
+    <row r="383">
+      <c r="B383" s="29"/>
+    </row>
+    <row r="384">
+      <c r="B384" s="29"/>
+    </row>
+    <row r="385">
+      <c r="B385" s="29"/>
+    </row>
+    <row r="386">
+      <c r="B386" s="29"/>
+    </row>
+    <row r="387">
+      <c r="B387" s="29"/>
+    </row>
+    <row r="388">
+      <c r="B388" s="29"/>
+    </row>
+    <row r="389">
+      <c r="B389" s="29"/>
+    </row>
+    <row r="390">
+      <c r="B390" s="29"/>
+    </row>
+    <row r="391">
+      <c r="B391" s="29"/>
+    </row>
+    <row r="392">
+      <c r="B392" s="29"/>
+    </row>
+    <row r="393">
+      <c r="B393" s="29"/>
+    </row>
+    <row r="394">
+      <c r="B394" s="29"/>
+    </row>
+    <row r="395">
+      <c r="B395" s="29"/>
+    </row>
+    <row r="396">
+      <c r="B396" s="29"/>
+    </row>
+    <row r="397">
+      <c r="B397" s="29"/>
+    </row>
+    <row r="398">
+      <c r="B398" s="29"/>
+    </row>
+    <row r="399">
+      <c r="B399" s="29"/>
+    </row>
+    <row r="400">
+      <c r="B400" s="29"/>
+    </row>
+    <row r="401">
+      <c r="B401" s="29"/>
+    </row>
+    <row r="402">
+      <c r="B402" s="29"/>
+    </row>
+    <row r="403">
+      <c r="B403" s="29"/>
+    </row>
+    <row r="404">
+      <c r="B404" s="29"/>
+    </row>
+    <row r="405">
+      <c r="B405" s="29"/>
+    </row>
+    <row r="406">
+      <c r="B406" s="29"/>
+    </row>
+    <row r="407">
+      <c r="B407" s="29"/>
+    </row>
+    <row r="408">
+      <c r="B408" s="29"/>
+    </row>
+    <row r="409">
+      <c r="B409" s="29"/>
+    </row>
+    <row r="410">
+      <c r="B410" s="29"/>
+    </row>
+    <row r="411">
+      <c r="B411" s="29"/>
+    </row>
+    <row r="412">
+      <c r="B412" s="29"/>
+    </row>
+    <row r="413">
+      <c r="B413" s="29"/>
+    </row>
+    <row r="414">
+      <c r="B414" s="29"/>
+    </row>
+    <row r="415">
+      <c r="B415" s="29"/>
+    </row>
+    <row r="416">
+      <c r="B416" s="29"/>
+    </row>
+    <row r="417">
+      <c r="B417" s="29"/>
+    </row>
+    <row r="418">
+      <c r="B418" s="29"/>
+    </row>
+    <row r="419">
+      <c r="B419" s="29"/>
+    </row>
+    <row r="420">
+      <c r="B420" s="29"/>
+    </row>
+    <row r="421">
+      <c r="B421" s="29"/>
+    </row>
+    <row r="422">
+      <c r="B422" s="29"/>
+    </row>
+    <row r="423">
+      <c r="B423" s="29"/>
+    </row>
+    <row r="424">
+      <c r="B424" s="29"/>
+    </row>
+    <row r="425">
+      <c r="B425" s="29"/>
+    </row>
+    <row r="426">
+      <c r="B426" s="29"/>
+    </row>
+    <row r="427">
+      <c r="B427" s="29"/>
+    </row>
+    <row r="428">
+      <c r="B428" s="29"/>
+    </row>
+    <row r="429">
+      <c r="B429" s="29"/>
+    </row>
+    <row r="430">
+      <c r="B430" s="29"/>
+    </row>
+    <row r="431">
+      <c r="B431" s="29"/>
+    </row>
+    <row r="432">
+      <c r="B432" s="29"/>
+    </row>
+    <row r="433">
+      <c r="B433" s="29"/>
+    </row>
+    <row r="434">
+      <c r="B434" s="29"/>
+    </row>
+    <row r="435">
+      <c r="B435" s="29"/>
+    </row>
+    <row r="436">
+      <c r="B436" s="29"/>
+    </row>
+    <row r="437">
+      <c r="B437" s="29"/>
+    </row>
+    <row r="438">
+      <c r="B438" s="29"/>
+    </row>
+    <row r="439">
+      <c r="B439" s="29"/>
+    </row>
+    <row r="440">
+      <c r="B440" s="29"/>
+    </row>
+    <row r="441">
+      <c r="B441" s="29"/>
+    </row>
+    <row r="442">
+      <c r="B442" s="29"/>
+    </row>
+    <row r="443">
+      <c r="B443" s="29"/>
+    </row>
+    <row r="444">
+      <c r="B444" s="29"/>
+    </row>
+    <row r="445">
+      <c r="B445" s="29"/>
+    </row>
+    <row r="446">
+      <c r="B446" s="29"/>
+    </row>
+    <row r="447">
+      <c r="B447" s="29"/>
+    </row>
+    <row r="448">
+      <c r="B448" s="29"/>
+    </row>
+    <row r="449">
+      <c r="B449" s="29"/>
+    </row>
+    <row r="450">
+      <c r="B450" s="29"/>
+    </row>
+    <row r="451">
+      <c r="B451" s="29"/>
+    </row>
+    <row r="452">
+      <c r="B452" s="29"/>
+    </row>
+    <row r="453">
+      <c r="B453" s="29"/>
+    </row>
+    <row r="454">
+      <c r="B454" s="29"/>
+    </row>
+    <row r="455">
+      <c r="B455" s="29"/>
+    </row>
+    <row r="456">
+      <c r="B456" s="29"/>
+    </row>
+    <row r="457">
+      <c r="B457" s="29"/>
+    </row>
+    <row r="458">
+      <c r="B458" s="29"/>
+    </row>
+    <row r="459">
+      <c r="B459" s="29"/>
+    </row>
+    <row r="460">
+      <c r="B460" s="29"/>
+    </row>
+    <row r="461">
+      <c r="B461" s="29"/>
+    </row>
+    <row r="462">
+      <c r="B462" s="29"/>
+    </row>
+    <row r="463">
+      <c r="B463" s="29"/>
+    </row>
+    <row r="464">
+      <c r="B464" s="29"/>
+    </row>
+    <row r="465">
+      <c r="B465" s="29"/>
+    </row>
+    <row r="466">
+      <c r="B466" s="29"/>
+    </row>
+    <row r="467">
+      <c r="B467" s="29"/>
+    </row>
+    <row r="468">
+      <c r="B468" s="29"/>
+    </row>
+    <row r="469">
+      <c r="B469" s="29"/>
+    </row>
+    <row r="470">
+      <c r="B470" s="29"/>
+    </row>
+    <row r="471">
+      <c r="B471" s="29"/>
+    </row>
+    <row r="472">
+      <c r="B472" s="29"/>
+    </row>
+    <row r="473">
+      <c r="B473" s="29"/>
+    </row>
+    <row r="474">
+      <c r="B474" s="29"/>
+    </row>
+    <row r="475">
+      <c r="B475" s="29"/>
+    </row>
+    <row r="476">
+      <c r="B476" s="29"/>
+    </row>
+    <row r="477">
+      <c r="B477" s="29"/>
+    </row>
+    <row r="478">
+      <c r="B478" s="29"/>
+    </row>
+    <row r="479">
+      <c r="B479" s="29"/>
+    </row>
+    <row r="480">
+      <c r="B480" s="29"/>
+    </row>
+    <row r="481">
+      <c r="B481" s="29"/>
+    </row>
+    <row r="482">
+      <c r="B482" s="29"/>
+    </row>
+    <row r="483">
+      <c r="B483" s="29"/>
+    </row>
+    <row r="484">
+      <c r="B484" s="29"/>
+    </row>
+    <row r="485">
+      <c r="B485" s="29"/>
+    </row>
+    <row r="486">
+      <c r="B486" s="29"/>
+    </row>
+    <row r="487">
+      <c r="B487" s="29"/>
+    </row>
+    <row r="488">
+      <c r="B488" s="29"/>
+    </row>
+    <row r="489">
+      <c r="B489" s="29"/>
+    </row>
+    <row r="490">
+      <c r="B490" s="29"/>
+    </row>
+    <row r="491">
+      <c r="B491" s="29"/>
+    </row>
+    <row r="492">
+      <c r="B492" s="29"/>
+    </row>
+    <row r="493">
+      <c r="B493" s="29"/>
+    </row>
+    <row r="494">
+      <c r="B494" s="29"/>
+    </row>
+    <row r="495">
+      <c r="B495" s="29"/>
+    </row>
+    <row r="496">
+      <c r="B496" s="29"/>
+    </row>
+    <row r="497">
+      <c r="B497" s="29"/>
+    </row>
+    <row r="498">
+      <c r="B498" s="29"/>
+    </row>
+    <row r="499">
+      <c r="B499" s="29"/>
+    </row>
+    <row r="500">
+      <c r="B500" s="29"/>
+    </row>
+    <row r="501">
+      <c r="B501" s="29"/>
+    </row>
+    <row r="502">
+      <c r="B502" s="29"/>
+    </row>
+    <row r="503">
+      <c r="B503" s="29"/>
+    </row>
+    <row r="504">
+      <c r="B504" s="29"/>
+    </row>
+    <row r="505">
+      <c r="B505" s="29"/>
+    </row>
+    <row r="506">
+      <c r="B506" s="29"/>
+    </row>
+    <row r="507">
+      <c r="B507" s="29"/>
+    </row>
+    <row r="508">
+      <c r="B508" s="29"/>
+    </row>
+    <row r="509">
+      <c r="B509" s="29"/>
+    </row>
+    <row r="510">
+      <c r="B510" s="29"/>
+    </row>
+    <row r="511">
+      <c r="B511" s="29"/>
+    </row>
+    <row r="512">
+      <c r="B512" s="29"/>
+    </row>
+    <row r="513">
+      <c r="B513" s="29"/>
+    </row>
+    <row r="514">
+      <c r="B514" s="29"/>
+    </row>
+    <row r="515">
+      <c r="B515" s="29"/>
+    </row>
+    <row r="516">
+      <c r="B516" s="29"/>
+    </row>
+    <row r="517">
+      <c r="B517" s="29"/>
+    </row>
+    <row r="518">
+      <c r="B518" s="29"/>
+    </row>
+    <row r="519">
+      <c r="B519" s="29"/>
+    </row>
+    <row r="520">
+      <c r="B520" s="29"/>
+    </row>
+    <row r="521">
+      <c r="B521" s="29"/>
+    </row>
+    <row r="522">
+      <c r="B522" s="29"/>
+    </row>
+    <row r="523">
+      <c r="B523" s="29"/>
+    </row>
+    <row r="524">
+      <c r="B524" s="29"/>
+    </row>
+    <row r="525">
+      <c r="B525" s="29"/>
+    </row>
+    <row r="526">
+      <c r="B526" s="29"/>
+    </row>
+    <row r="527">
+      <c r="B527" s="29"/>
+    </row>
+    <row r="528">
+      <c r="B528" s="29"/>
+    </row>
+    <row r="529">
+      <c r="B529" s="29"/>
+    </row>
+    <row r="530">
+      <c r="B530" s="29"/>
+    </row>
+    <row r="531">
+      <c r="B531" s="29"/>
+    </row>
+    <row r="532">
+      <c r="B532" s="29"/>
+    </row>
+    <row r="533">
+      <c r="B533" s="29"/>
+    </row>
+    <row r="534">
+      <c r="B534" s="29"/>
+    </row>
+    <row r="535">
+      <c r="B535" s="29"/>
+    </row>
+    <row r="536">
+      <c r="B536" s="29"/>
+    </row>
+    <row r="537">
+      <c r="B537" s="29"/>
+    </row>
+    <row r="538">
+      <c r="B538" s="29"/>
+    </row>
+    <row r="539">
+      <c r="B539" s="29"/>
+    </row>
+    <row r="540">
+      <c r="B540" s="29"/>
+    </row>
+    <row r="541">
+      <c r="B541" s="29"/>
+    </row>
+    <row r="542">
+      <c r="B542" s="29"/>
+    </row>
+    <row r="543">
+      <c r="B543" s="29"/>
+    </row>
+    <row r="544">
+      <c r="B544" s="29"/>
+    </row>
+    <row r="545">
+      <c r="B545" s="29"/>
+    </row>
+    <row r="546">
+      <c r="B546" s="29"/>
+    </row>
+    <row r="547">
+      <c r="B547" s="29"/>
+    </row>
+    <row r="548">
+      <c r="B548" s="29"/>
+    </row>
+    <row r="549">
+      <c r="B549" s="29"/>
+    </row>
+    <row r="550">
+      <c r="B550" s="29"/>
+    </row>
+    <row r="551">
+      <c r="B551" s="29"/>
+    </row>
+    <row r="552">
+      <c r="B552" s="29"/>
+    </row>
+    <row r="553">
+      <c r="B553" s="29"/>
+    </row>
+    <row r="554">
+      <c r="B554" s="29"/>
+    </row>
+    <row r="555">
+      <c r="B555" s="29"/>
+    </row>
+    <row r="556">
+      <c r="B556" s="29"/>
+    </row>
+    <row r="557">
+      <c r="B557" s="29"/>
+    </row>
+    <row r="558">
+      <c r="B558" s="29"/>
+    </row>
+    <row r="559">
+      <c r="B559" s="29"/>
+    </row>
+    <row r="560">
+      <c r="B560" s="29"/>
+    </row>
+    <row r="561">
+      <c r="B561" s="29"/>
+    </row>
+    <row r="562">
+      <c r="B562" s="29"/>
+    </row>
+    <row r="563">
+      <c r="B563" s="29"/>
+    </row>
+    <row r="564">
+      <c r="B564" s="29"/>
+    </row>
+    <row r="565">
+      <c r="B565" s="29"/>
+    </row>
+    <row r="566">
+      <c r="B566" s="29"/>
+    </row>
+    <row r="567">
+      <c r="B567" s="29"/>
+    </row>
+    <row r="568">
+      <c r="B568" s="29"/>
+    </row>
+    <row r="569">
+      <c r="B569" s="29"/>
+    </row>
+    <row r="570">
+      <c r="B570" s="29"/>
+    </row>
+    <row r="571">
+      <c r="B571" s="29"/>
+    </row>
+    <row r="572">
+      <c r="B572" s="29"/>
+    </row>
+    <row r="573">
+      <c r="B573" s="29"/>
+    </row>
+    <row r="574">
+      <c r="B574" s="29"/>
+    </row>
+    <row r="575">
+      <c r="B575" s="29"/>
+    </row>
+    <row r="576">
+      <c r="B576" s="29"/>
+    </row>
+    <row r="577">
+      <c r="B577" s="29"/>
+    </row>
+    <row r="578">
+      <c r="B578" s="29"/>
+    </row>
+    <row r="579">
+      <c r="B579" s="29"/>
+    </row>
+    <row r="580">
+      <c r="B580" s="29"/>
+    </row>
+    <row r="581">
+      <c r="B581" s="29"/>
+    </row>
+    <row r="582">
+      <c r="B582" s="29"/>
+    </row>
+    <row r="583">
+      <c r="B583" s="29"/>
+    </row>
+    <row r="584">
+      <c r="B584" s="29"/>
+    </row>
+    <row r="585">
+      <c r="B585" s="29"/>
+    </row>
+    <row r="586">
+      <c r="B586" s="29"/>
+    </row>
+    <row r="587">
+      <c r="B587" s="29"/>
+    </row>
+    <row r="588">
+      <c r="B588" s="29"/>
+    </row>
+    <row r="589">
+      <c r="B589" s="29"/>
+    </row>
+    <row r="590">
+      <c r="B590" s="29"/>
+    </row>
+    <row r="591">
+      <c r="B591" s="29"/>
+    </row>
+    <row r="592">
+      <c r="B592" s="29"/>
+    </row>
+    <row r="593">
+      <c r="B593" s="29"/>
+    </row>
+    <row r="594">
+      <c r="B594" s="29"/>
+    </row>
+    <row r="595">
+      <c r="B595" s="29"/>
+    </row>
+    <row r="596">
+      <c r="B596" s="29"/>
+    </row>
+    <row r="597">
+      <c r="B597" s="29"/>
+    </row>
+    <row r="598">
+      <c r="B598" s="29"/>
+    </row>
+    <row r="599">
+      <c r="B599" s="29"/>
+    </row>
+    <row r="600">
+      <c r="B600" s="29"/>
+    </row>
+    <row r="601">
+      <c r="B601" s="29"/>
+    </row>
+    <row r="602">
+      <c r="B602" s="29"/>
+    </row>
+    <row r="603">
+      <c r="B603" s="29"/>
+    </row>
+    <row r="604">
+      <c r="B604" s="29"/>
+    </row>
+    <row r="605">
+      <c r="B605" s="29"/>
+    </row>
+    <row r="606">
+      <c r="B606" s="29"/>
+    </row>
+    <row r="607">
+      <c r="B607" s="29"/>
+    </row>
+    <row r="608">
+      <c r="B608" s="29"/>
+    </row>
+    <row r="609">
+      <c r="B609" s="29"/>
+    </row>
+    <row r="610">
+      <c r="B610" s="29"/>
+    </row>
+    <row r="611">
+      <c r="B611" s="29"/>
+    </row>
+    <row r="612">
+      <c r="B612" s="29"/>
+    </row>
+    <row r="613">
+      <c r="B613" s="29"/>
+    </row>
+    <row r="614">
+      <c r="B614" s="29"/>
+    </row>
+    <row r="615">
+      <c r="B615" s="29"/>
+    </row>
+    <row r="616">
+      <c r="B616" s="29"/>
+    </row>
+    <row r="617">
+      <c r="B617" s="29"/>
+    </row>
+    <row r="618">
+      <c r="B618" s="29"/>
+    </row>
+    <row r="619">
+      <c r="B619" s="29"/>
+    </row>
+    <row r="620">
+      <c r="B620" s="29"/>
+    </row>
+    <row r="621">
+      <c r="B621" s="29"/>
+    </row>
+    <row r="622">
+      <c r="B622" s="29"/>
+    </row>
+    <row r="623">
+      <c r="B623" s="29"/>
+    </row>
+    <row r="624">
+      <c r="B624" s="29"/>
+    </row>
+    <row r="625">
+      <c r="B625" s="29"/>
+    </row>
+    <row r="626">
+      <c r="B626" s="29"/>
+    </row>
+    <row r="627">
+      <c r="B627" s="29"/>
+    </row>
+    <row r="628">
+      <c r="B628" s="29"/>
+    </row>
+    <row r="629">
+      <c r="B629" s="29"/>
+    </row>
+    <row r="630">
+      <c r="B630" s="29"/>
+    </row>
+    <row r="631">
+      <c r="B631" s="29"/>
+    </row>
+    <row r="632">
+      <c r="B632" s="29"/>
+    </row>
+    <row r="633">
+      <c r="B633" s="29"/>
+    </row>
+    <row r="634">
+      <c r="B634" s="29"/>
+    </row>
+    <row r="635">
+      <c r="B635" s="29"/>
+    </row>
+    <row r="636">
+      <c r="B636" s="29"/>
+    </row>
+    <row r="637">
+      <c r="B637" s="29"/>
+    </row>
+    <row r="638">
+      <c r="B638" s="29"/>
+    </row>
+    <row r="639">
+      <c r="B639" s="29"/>
+    </row>
+    <row r="640">
+      <c r="B640" s="29"/>
+    </row>
+    <row r="641">
+      <c r="B641" s="29"/>
+    </row>
+    <row r="642">
+      <c r="B642" s="29"/>
+    </row>
+    <row r="643">
+      <c r="B643" s="29"/>
+    </row>
+    <row r="644">
+      <c r="B644" s="29"/>
+    </row>
+    <row r="645">
+      <c r="B645" s="29"/>
+    </row>
+    <row r="646">
+      <c r="B646" s="29"/>
+    </row>
+    <row r="647">
+      <c r="B647" s="29"/>
+    </row>
+    <row r="648">
+      <c r="B648" s="29"/>
+    </row>
+    <row r="649">
+      <c r="B649" s="29"/>
+    </row>
+    <row r="650">
+      <c r="B650" s="29"/>
+    </row>
+    <row r="651">
+      <c r="B651" s="29"/>
+    </row>
+    <row r="652">
+      <c r="B652" s="29"/>
+    </row>
+    <row r="653">
+      <c r="B653" s="29"/>
+    </row>
+    <row r="654">
+      <c r="B654" s="29"/>
+    </row>
+    <row r="655">
+      <c r="B655" s="29"/>
+    </row>
+    <row r="656">
+      <c r="B656" s="29"/>
+    </row>
+    <row r="657">
+      <c r="B657" s="29"/>
+    </row>
+    <row r="658">
+      <c r="B658" s="29"/>
+    </row>
+    <row r="659">
+      <c r="B659" s="29"/>
+    </row>
+    <row r="660">
+      <c r="B660" s="29"/>
+    </row>
+    <row r="661">
+      <c r="B661" s="29"/>
+    </row>
+    <row r="662">
+      <c r="B662" s="29"/>
+    </row>
+    <row r="663">
+      <c r="B663" s="29"/>
+    </row>
+    <row r="664">
+      <c r="B664" s="29"/>
+    </row>
+    <row r="665">
+      <c r="B665" s="29"/>
+    </row>
+    <row r="666">
+      <c r="B666" s="29"/>
+    </row>
+    <row r="667">
+      <c r="B667" s="29"/>
+    </row>
+    <row r="668">
+      <c r="B668" s="29"/>
+    </row>
+    <row r="669">
+      <c r="B669" s="29"/>
+    </row>
+    <row r="670">
+      <c r="B670" s="29"/>
+    </row>
+    <row r="671">
+      <c r="B671" s="29"/>
+    </row>
+    <row r="672">
+      <c r="B672" s="29"/>
+    </row>
+    <row r="673">
+      <c r="B673" s="29"/>
+    </row>
+    <row r="674">
+      <c r="B674" s="29"/>
+    </row>
+    <row r="675">
+      <c r="B675" s="29"/>
+    </row>
+    <row r="676">
+      <c r="B676" s="29"/>
+    </row>
+    <row r="677">
+      <c r="B677" s="29"/>
+    </row>
+    <row r="678">
+      <c r="B678" s="29"/>
+    </row>
+    <row r="679">
+      <c r="B679" s="29"/>
+    </row>
+    <row r="680">
+      <c r="B680" s="29"/>
+    </row>
+    <row r="681">
+      <c r="B681" s="29"/>
+    </row>
+    <row r="682">
+      <c r="B682" s="29"/>
+    </row>
+    <row r="683">
+      <c r="B683" s="29"/>
+    </row>
+    <row r="684">
+      <c r="B684" s="29"/>
+    </row>
+    <row r="685">
+      <c r="B685" s="29"/>
+    </row>
+    <row r="686">
+      <c r="B686" s="29"/>
+    </row>
+    <row r="687">
+      <c r="B687" s="29"/>
+    </row>
+    <row r="688">
+      <c r="B688" s="29"/>
+    </row>
+    <row r="689">
+      <c r="B689" s="29"/>
+    </row>
+    <row r="690">
+      <c r="B690" s="29"/>
+    </row>
+    <row r="691">
+      <c r="B691" s="29"/>
+    </row>
+    <row r="692">
+      <c r="B692" s="29"/>
+    </row>
+    <row r="693">
+      <c r="B693" s="29"/>
+    </row>
+    <row r="694">
+      <c r="B694" s="29"/>
+    </row>
+    <row r="695">
+      <c r="B695" s="29"/>
+    </row>
+    <row r="696">
+      <c r="B696" s="29"/>
+    </row>
+    <row r="697">
+      <c r="B697" s="29"/>
+    </row>
+    <row r="698">
+      <c r="B698" s="29"/>
+    </row>
+    <row r="699">
+      <c r="B699" s="29"/>
+    </row>
+    <row r="700">
+      <c r="B700" s="29"/>
+    </row>
+    <row r="701">
+      <c r="B701" s="29"/>
+    </row>
+    <row r="702">
+      <c r="B702" s="29"/>
+    </row>
+    <row r="703">
+      <c r="B703" s="29"/>
+    </row>
+    <row r="704">
+      <c r="B704" s="29"/>
+    </row>
+    <row r="705">
+      <c r="B705" s="29"/>
+    </row>
+    <row r="706">
+      <c r="B706" s="29"/>
+    </row>
+    <row r="707">
+      <c r="B707" s="29"/>
+    </row>
+    <row r="708">
+      <c r="B708" s="29"/>
+    </row>
+    <row r="709">
+      <c r="B709" s="29"/>
+    </row>
+    <row r="710">
+      <c r="B710" s="29"/>
+    </row>
+    <row r="711">
+      <c r="B711" s="29"/>
+    </row>
+    <row r="712">
+      <c r="B712" s="29"/>
+    </row>
+    <row r="713">
+      <c r="B713" s="29"/>
+    </row>
+    <row r="714">
+      <c r="B714" s="29"/>
+    </row>
+    <row r="715">
+      <c r="B715" s="29"/>
+    </row>
+    <row r="716">
+      <c r="B716" s="29"/>
+    </row>
+    <row r="717">
+      <c r="B717" s="29"/>
+    </row>
+    <row r="718">
+      <c r="B718" s="29"/>
+    </row>
+    <row r="719">
+      <c r="B719" s="29"/>
+    </row>
+    <row r="720">
+      <c r="B720" s="29"/>
+    </row>
+    <row r="721">
+      <c r="B721" s="29"/>
+    </row>
+    <row r="722">
+      <c r="B722" s="29"/>
+    </row>
+    <row r="723">
+      <c r="B723" s="29"/>
+    </row>
+    <row r="724">
+      <c r="B724" s="29"/>
+    </row>
+    <row r="725">
+      <c r="B725" s="29"/>
+    </row>
+    <row r="726">
+      <c r="B726" s="29"/>
+    </row>
+    <row r="727">
+      <c r="B727" s="29"/>
+    </row>
+    <row r="728">
+      <c r="B728" s="29"/>
+    </row>
+    <row r="729">
+      <c r="B729" s="29"/>
+    </row>
+    <row r="730">
+      <c r="B730" s="29"/>
+    </row>
+    <row r="731">
+      <c r="B731" s="29"/>
+    </row>
+    <row r="732">
+      <c r="B732" s="29"/>
+    </row>
+    <row r="733">
+      <c r="B733" s="29"/>
+    </row>
+    <row r="734">
+      <c r="B734" s="29"/>
+    </row>
+    <row r="735">
+      <c r="B735" s="29"/>
+    </row>
+    <row r="736">
+      <c r="B736" s="29"/>
+    </row>
+    <row r="737">
+      <c r="B737" s="29"/>
+    </row>
+    <row r="738">
+      <c r="B738" s="29"/>
+    </row>
+    <row r="739">
+      <c r="B739" s="29"/>
+    </row>
+    <row r="740">
+      <c r="B740" s="29"/>
+    </row>
+    <row r="741">
+      <c r="B741" s="29"/>
+    </row>
+    <row r="742">
+      <c r="B742" s="29"/>
+    </row>
+    <row r="743">
+      <c r="B743" s="29"/>
+    </row>
+    <row r="744">
+      <c r="B744" s="29"/>
+    </row>
+    <row r="745">
+      <c r="B745" s="29"/>
+    </row>
+    <row r="746">
+      <c r="B746" s="29"/>
+    </row>
+    <row r="747">
+      <c r="B747" s="29"/>
+    </row>
+    <row r="748">
+      <c r="B748" s="29"/>
+    </row>
+    <row r="749">
+      <c r="B749" s="29"/>
+    </row>
+    <row r="750">
+      <c r="B750" s="29"/>
+    </row>
+    <row r="751">
+      <c r="B751" s="29"/>
+    </row>
+    <row r="752">
+      <c r="B752" s="29"/>
+    </row>
+    <row r="753">
+      <c r="B753" s="29"/>
+    </row>
+    <row r="754">
+      <c r="B754" s="29"/>
+    </row>
+    <row r="755">
+      <c r="B755" s="29"/>
+    </row>
+    <row r="756">
+      <c r="B756" s="29"/>
+    </row>
+    <row r="757">
+      <c r="B757" s="29"/>
+    </row>
+    <row r="758">
+      <c r="B758" s="29"/>
+    </row>
+    <row r="759">
+      <c r="B759" s="29"/>
+    </row>
+    <row r="760">
+      <c r="B760" s="29"/>
+    </row>
+    <row r="761">
+      <c r="B761" s="29"/>
+    </row>
+    <row r="762">
+      <c r="B762" s="29"/>
+    </row>
+    <row r="763">
+      <c r="B763" s="29"/>
+    </row>
+    <row r="764">
+      <c r="B764" s="29"/>
+    </row>
+    <row r="765">
+      <c r="B765" s="29"/>
+    </row>
+    <row r="766">
+      <c r="B766" s="29"/>
+    </row>
+    <row r="767">
+      <c r="B767" s="29"/>
+    </row>
+    <row r="768">
+      <c r="B768" s="29"/>
+    </row>
+    <row r="769">
+      <c r="B769" s="29"/>
+    </row>
+    <row r="770">
+      <c r="B770" s="29"/>
+    </row>
+    <row r="771">
+      <c r="B771" s="29"/>
+    </row>
+    <row r="772">
+      <c r="B772" s="29"/>
+    </row>
+    <row r="773">
+      <c r="B773" s="29"/>
+    </row>
+    <row r="774">
+      <c r="B774" s="29"/>
+    </row>
+    <row r="775">
+      <c r="B775" s="29"/>
+    </row>
+    <row r="776">
+      <c r="B776" s="29"/>
+    </row>
+    <row r="777">
+      <c r="B777" s="29"/>
+    </row>
+    <row r="778">
+      <c r="B778" s="29"/>
+    </row>
+    <row r="779">
+      <c r="B779" s="29"/>
+    </row>
+    <row r="780">
+      <c r="B780" s="29"/>
+    </row>
+    <row r="781">
+      <c r="B781" s="29"/>
+    </row>
+    <row r="782">
+      <c r="B782" s="29"/>
+    </row>
+    <row r="783">
+      <c r="B783" s="29"/>
+    </row>
+    <row r="784">
+      <c r="B784" s="29"/>
+    </row>
+    <row r="785">
+      <c r="B785" s="29"/>
+    </row>
+    <row r="786">
+      <c r="B786" s="29"/>
+    </row>
+    <row r="787">
+      <c r="B787" s="29"/>
+    </row>
+    <row r="788">
+      <c r="B788" s="29"/>
+    </row>
+    <row r="789">
+      <c r="B789" s="29"/>
+    </row>
+    <row r="790">
+      <c r="B790" s="29"/>
+    </row>
+    <row r="791">
+      <c r="B791" s="29"/>
+    </row>
+    <row r="792">
+      <c r="B792" s="29"/>
+    </row>
+    <row r="793">
+      <c r="B793" s="29"/>
+    </row>
+    <row r="794">
+      <c r="B794" s="29"/>
+    </row>
+    <row r="795">
+      <c r="B795" s="29"/>
+    </row>
+    <row r="796">
+      <c r="B796" s="29"/>
+    </row>
+    <row r="797">
+      <c r="B797" s="29"/>
+    </row>
+    <row r="798">
+      <c r="B798" s="29"/>
+    </row>
+    <row r="799">
+      <c r="B799" s="29"/>
+    </row>
+    <row r="800">
+      <c r="B800" s="29"/>
+    </row>
+    <row r="801">
+      <c r="B801" s="29"/>
+    </row>
+    <row r="802">
+      <c r="B802" s="29"/>
+    </row>
+    <row r="803">
+      <c r="B803" s="29"/>
+    </row>
+    <row r="804">
+      <c r="B804" s="29"/>
+    </row>
+    <row r="805">
+      <c r="B805" s="29"/>
+    </row>
+    <row r="806">
+      <c r="B806" s="29"/>
+    </row>
+    <row r="807">
+      <c r="B807" s="29"/>
+    </row>
+    <row r="808">
+      <c r="B808" s="29"/>
+    </row>
+    <row r="809">
+      <c r="B809" s="29"/>
+    </row>
+    <row r="810">
+      <c r="B810" s="29"/>
+    </row>
+    <row r="811">
+      <c r="B811" s="29"/>
+    </row>
+    <row r="812">
+      <c r="B812" s="29"/>
+    </row>
+    <row r="813">
+      <c r="B813" s="29"/>
+    </row>
+    <row r="814">
+      <c r="B814" s="29"/>
+    </row>
+    <row r="815">
+      <c r="B815" s="29"/>
+    </row>
+    <row r="816">
+      <c r="B816" s="29"/>
+    </row>
+    <row r="817">
+      <c r="B817" s="29"/>
+    </row>
+    <row r="818">
+      <c r="B818" s="29"/>
+    </row>
+    <row r="819">
+      <c r="B819" s="29"/>
+    </row>
+    <row r="820">
+      <c r="B820" s="29"/>
+    </row>
+    <row r="821">
+      <c r="B821" s="29"/>
+    </row>
+    <row r="822">
+      <c r="B822" s="29"/>
+    </row>
+    <row r="823">
+      <c r="B823" s="29"/>
+    </row>
+    <row r="824">
+      <c r="B824" s="29"/>
+    </row>
+    <row r="825">
+      <c r="B825" s="29"/>
+    </row>
+    <row r="826">
+      <c r="B826" s="29"/>
+    </row>
+    <row r="827">
+      <c r="B827" s="29"/>
+    </row>
+    <row r="828">
+      <c r="B828" s="29"/>
+    </row>
+    <row r="829">
+      <c r="B829" s="29"/>
+    </row>
+    <row r="830">
+      <c r="B830" s="29"/>
+    </row>
+    <row r="831">
+      <c r="B831" s="29"/>
+    </row>
+    <row r="832">
+      <c r="B832" s="29"/>
+    </row>
+    <row r="833">
+      <c r="B833" s="29"/>
+    </row>
+    <row r="834">
+      <c r="B834" s="29"/>
+    </row>
+    <row r="835">
+      <c r="B835" s="29"/>
+    </row>
+    <row r="836">
+      <c r="B836" s="29"/>
+    </row>
+    <row r="837">
+      <c r="B837" s="29"/>
+    </row>
+    <row r="838">
+      <c r="B838" s="29"/>
+    </row>
+    <row r="839">
+      <c r="B839" s="29"/>
+    </row>
+    <row r="840">
+      <c r="B840" s="29"/>
+    </row>
+    <row r="841">
+      <c r="B841" s="29"/>
+    </row>
+    <row r="842">
+      <c r="B842" s="29"/>
+    </row>
+    <row r="843">
+      <c r="B843" s="29"/>
+    </row>
+    <row r="844">
+      <c r="B844" s="29"/>
+    </row>
+    <row r="845">
+      <c r="B845" s="29"/>
+    </row>
+    <row r="846">
+      <c r="B846" s="29"/>
+    </row>
+    <row r="847">
+      <c r="B847" s="29"/>
+    </row>
+    <row r="848">
+      <c r="B848" s="29"/>
+    </row>
+    <row r="849">
+      <c r="B849" s="29"/>
+    </row>
+    <row r="850">
+      <c r="B850" s="29"/>
+    </row>
+    <row r="851">
+      <c r="B851" s="29"/>
+    </row>
+    <row r="852">
+      <c r="B852" s="29"/>
+    </row>
+    <row r="853">
+      <c r="B853" s="29"/>
+    </row>
+    <row r="854">
+      <c r="B854" s="29"/>
+    </row>
+    <row r="855">
+      <c r="B855" s="29"/>
+    </row>
+    <row r="856">
+      <c r="B856" s="29"/>
+    </row>
+    <row r="857">
+      <c r="B857" s="29"/>
+    </row>
+    <row r="858">
+      <c r="B858" s="29"/>
+    </row>
+    <row r="859">
+      <c r="B859" s="29"/>
+    </row>
+    <row r="860">
+      <c r="B860" s="29"/>
+    </row>
+    <row r="861">
+      <c r="B861" s="29"/>
+    </row>
+    <row r="862">
+      <c r="B862" s="29"/>
+    </row>
+    <row r="863">
+      <c r="B863" s="29"/>
+    </row>
+    <row r="864">
+      <c r="B864" s="29"/>
+    </row>
+    <row r="865">
+      <c r="B865" s="29"/>
+    </row>
+    <row r="866">
+      <c r="B866" s="29"/>
+    </row>
+    <row r="867">
+      <c r="B867" s="29"/>
+    </row>
+    <row r="868">
+      <c r="B868" s="29"/>
+    </row>
+    <row r="869">
+      <c r="B869" s="29"/>
+    </row>
+    <row r="870">
+      <c r="B870" s="29"/>
+    </row>
+    <row r="871">
+      <c r="B871" s="29"/>
+    </row>
+    <row r="872">
+      <c r="B872" s="29"/>
+    </row>
+    <row r="873">
+      <c r="B873" s="29"/>
+    </row>
+    <row r="874">
+      <c r="B874" s="29"/>
+    </row>
+    <row r="875">
+      <c r="B875" s="29"/>
+    </row>
+    <row r="876">
+      <c r="B876" s="29"/>
+    </row>
+    <row r="877">
+      <c r="B877" s="29"/>
+    </row>
+    <row r="878">
+      <c r="B878" s="29"/>
+    </row>
+    <row r="879">
+      <c r="B879" s="29"/>
+    </row>
+    <row r="880">
+      <c r="B880" s="29"/>
+    </row>
+    <row r="881">
+      <c r="B881" s="29"/>
+    </row>
+    <row r="882">
+      <c r="B882" s="29"/>
+    </row>
+    <row r="883">
+      <c r="B883" s="29"/>
+    </row>
+    <row r="884">
+      <c r="B884" s="29"/>
+    </row>
+    <row r="885">
+      <c r="B885" s="29"/>
+    </row>
+    <row r="886">
+      <c r="B886" s="29"/>
+    </row>
+    <row r="887">
+      <c r="B887" s="29"/>
+    </row>
+    <row r="888">
+      <c r="B888" s="29"/>
+    </row>
+    <row r="889">
+      <c r="B889" s="29"/>
+    </row>
+    <row r="890">
+      <c r="B890" s="29"/>
+    </row>
+    <row r="891">
+      <c r="B891" s="29"/>
+    </row>
+    <row r="892">
+      <c r="B892" s="29"/>
+    </row>
+    <row r="893">
+      <c r="B893" s="29"/>
+    </row>
+    <row r="894">
+      <c r="B894" s="29"/>
+    </row>
+    <row r="895">
+      <c r="B895" s="29"/>
+    </row>
+    <row r="896">
+      <c r="B896" s="29"/>
+    </row>
+    <row r="897">
+      <c r="B897" s="29"/>
+    </row>
+    <row r="898">
+      <c r="B898" s="29"/>
+    </row>
+    <row r="899">
+      <c r="B899" s="29"/>
+    </row>
+    <row r="900">
+      <c r="B900" s="29"/>
+    </row>
+    <row r="901">
+      <c r="B901" s="29"/>
+    </row>
+    <row r="902">
+      <c r="B902" s="29"/>
+    </row>
+    <row r="903">
+      <c r="B903" s="29"/>
+    </row>
+    <row r="904">
+      <c r="B904" s="29"/>
+    </row>
+    <row r="905">
+      <c r="B905" s="29"/>
+    </row>
+    <row r="906">
+      <c r="B906" s="29"/>
+    </row>
+    <row r="907">
+      <c r="B907" s="29"/>
+    </row>
+    <row r="908">
+      <c r="B908" s="29"/>
+    </row>
+    <row r="909">
+      <c r="B909" s="29"/>
+    </row>
+    <row r="910">
+      <c r="B910" s="29"/>
+    </row>
+    <row r="911">
+      <c r="B911" s="29"/>
+    </row>
+    <row r="912">
+      <c r="B912" s="29"/>
+    </row>
+    <row r="913">
+      <c r="B913" s="29"/>
+    </row>
+    <row r="914">
+      <c r="B914" s="29"/>
+    </row>
+    <row r="915">
+      <c r="B915" s="29"/>
+    </row>
+    <row r="916">
+      <c r="B916" s="29"/>
+    </row>
+    <row r="917">
+      <c r="B917" s="29"/>
+    </row>
+    <row r="918">
+      <c r="B918" s="29"/>
+    </row>
+    <row r="919">
+      <c r="B919" s="29"/>
+    </row>
+    <row r="920">
+      <c r="B920" s="29"/>
+    </row>
+    <row r="921">
+      <c r="B921" s="29"/>
+    </row>
+    <row r="922">
+      <c r="B922" s="29"/>
+    </row>
+    <row r="923">
+      <c r="B923" s="29"/>
+    </row>
+    <row r="924">
+      <c r="B924" s="29"/>
+    </row>
+    <row r="925">
+      <c r="B925" s="29"/>
+    </row>
+    <row r="926">
+      <c r="B926" s="29"/>
+    </row>
+    <row r="927">
+      <c r="B927" s="29"/>
+    </row>
+    <row r="928">
+      <c r="B928" s="29"/>
+    </row>
+    <row r="929">
+      <c r="B929" s="29"/>
+    </row>
+    <row r="930">
+      <c r="B930" s="29"/>
+    </row>
+    <row r="931">
+      <c r="B931" s="29"/>
+    </row>
+    <row r="932">
+      <c r="B932" s="29"/>
+    </row>
+    <row r="933">
+      <c r="B933" s="29"/>
+    </row>
+    <row r="934">
+      <c r="B934" s="29"/>
+    </row>
+    <row r="935">
+      <c r="B935" s="29"/>
+    </row>
+    <row r="936">
+      <c r="B936" s="29"/>
+    </row>
+    <row r="937">
+      <c r="B937" s="29"/>
+    </row>
+    <row r="938">
+      <c r="B938" s="29"/>
+    </row>
+    <row r="939">
+      <c r="B939" s="29"/>
+    </row>
+    <row r="940">
+      <c r="B940" s="29"/>
+    </row>
+    <row r="941">
+      <c r="B941" s="29"/>
+    </row>
+    <row r="942">
+      <c r="B942" s="29"/>
+    </row>
+    <row r="943">
+      <c r="B943" s="29"/>
+    </row>
+    <row r="944">
+      <c r="B944" s="29"/>
+    </row>
+    <row r="945">
+      <c r="B945" s="29"/>
+    </row>
+    <row r="946">
+      <c r="B946" s="29"/>
+    </row>
+    <row r="947">
+      <c r="B947" s="29"/>
+    </row>
+    <row r="948">
+      <c r="B948" s="29"/>
+    </row>
+    <row r="949">
+      <c r="B949" s="29"/>
+    </row>
+    <row r="950">
+      <c r="B950" s="29"/>
+    </row>
+    <row r="951">
+      <c r="B951" s="29"/>
+    </row>
+    <row r="952">
+      <c r="B952" s="29"/>
+    </row>
+    <row r="953">
+      <c r="B953" s="29"/>
+    </row>
+    <row r="954">
+      <c r="B954" s="29"/>
+    </row>
+    <row r="955">
+      <c r="B955" s="29"/>
+    </row>
+    <row r="956">
+      <c r="B956" s="29"/>
+    </row>
+    <row r="957">
+      <c r="B957" s="29"/>
+    </row>
+    <row r="958">
+      <c r="B958" s="29"/>
+    </row>
+    <row r="959">
+      <c r="B959" s="29"/>
+    </row>
+    <row r="960">
+      <c r="B960" s="29"/>
+    </row>
+    <row r="961">
+      <c r="B961" s="29"/>
+    </row>
+    <row r="962">
+      <c r="B962" s="29"/>
+    </row>
+    <row r="963">
+      <c r="B963" s="29"/>
+    </row>
+    <row r="964">
+      <c r="B964" s="29"/>
+    </row>
+    <row r="965">
+      <c r="B965" s="29"/>
+    </row>
+    <row r="966">
+      <c r="B966" s="29"/>
+    </row>
+    <row r="967">
+      <c r="B967" s="29"/>
+    </row>
+    <row r="968">
+      <c r="B968" s="29"/>
+    </row>
+    <row r="969">
+      <c r="B969" s="29"/>
+    </row>
+    <row r="970">
+      <c r="B970" s="29"/>
+    </row>
+    <row r="971">
+      <c r="B971" s="29"/>
+    </row>
+    <row r="972">
+      <c r="B972" s="29"/>
+    </row>
+    <row r="973">
+      <c r="B973" s="29"/>
+    </row>
+    <row r="974">
+      <c r="B974" s="29"/>
+    </row>
+    <row r="975">
+      <c r="B975" s="29"/>
+    </row>
+    <row r="976">
+      <c r="B976" s="29"/>
+    </row>
+    <row r="977">
+      <c r="B977" s="29"/>
+    </row>
+    <row r="978">
+      <c r="B978" s="29"/>
+    </row>
+    <row r="979">
+      <c r="B979" s="29"/>
+    </row>
+    <row r="980">
+      <c r="B980" s="29"/>
+    </row>
+    <row r="981">
+      <c r="B981" s="29"/>
+    </row>
+    <row r="982">
+      <c r="B982" s="29"/>
+    </row>
+    <row r="983">
+      <c r="B983" s="29"/>
+    </row>
+    <row r="984">
+      <c r="B984" s="29"/>
+    </row>
+    <row r="985">
+      <c r="B985" s="29"/>
+    </row>
+    <row r="986">
+      <c r="B986" s="29"/>
+    </row>
+    <row r="987">
+      <c r="B987" s="29"/>
+    </row>
+    <row r="988">
+      <c r="B988" s="29"/>
+    </row>
+    <row r="989">
+      <c r="B989" s="29"/>
+    </row>
+    <row r="990">
+      <c r="B990" s="29"/>
+    </row>
+    <row r="991">
+      <c r="B991" s="29"/>
+    </row>
+    <row r="992">
+      <c r="B992" s="29"/>
+    </row>
+    <row r="993">
+      <c r="B993" s="29"/>
+    </row>
+    <row r="994">
+      <c r="B994" s="29"/>
+    </row>
+    <row r="995">
+      <c r="B995" s="29"/>
+    </row>
+    <row r="996">
+      <c r="B996" s="29"/>
+    </row>
+    <row r="997">
+      <c r="B997" s="29"/>
+    </row>
+    <row r="998">
+      <c r="B998" s="29"/>
+    </row>
+    <row r="999">
+      <c r="B999" s="29"/>
+    </row>
+    <row r="1000">
+      <c r="B1000" s="29"/>
+    </row>
+    <row r="1001">
+      <c r="B1001" s="29"/>
+    </row>
+    <row r="1002">
+      <c r="B1002" s="29"/>
+    </row>
+    <row r="1003">
+      <c r="B1003" s="29"/>
+    </row>
+    <row r="1004">
+      <c r="B1004" s="29"/>
+    </row>
+    <row r="1005">
+      <c r="B1005" s="29"/>
+    </row>
+    <row r="1006">
+      <c r="B1006" s="29"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/src/data/Sources_and_Definitions.xlsx
+++ b/src/data/Sources_and_Definitions.xlsx
@@ -1540,7 +1540,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yy"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1556,24 +1556,17 @@
     </font>
     <font>
       <b/>
-      <sz val="8.0"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="8.0"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1646,61 +1639,8 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border/>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
     <border>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -1710,7 +1650,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="32">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1720,22 +1660,10 @@
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1744,73 +1672,70 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2046,4533 +1971,4533 @@
       <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="7">
         <v>44619.0</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="N2" s="10"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="N2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10" t="s">
+      <c r="H4" s="6"/>
+      <c r="I4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="10"/>
+      <c r="L4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="10">
         <v>45658.0</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="10">
         <v>45807.0</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="13" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="10">
         <v>45784.0</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="14" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="10">
         <v>45504.0</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="6" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="N10" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="N11" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="10">
         <v>45659.0</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="N12" s="10" t="s">
+      <c r="N12" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="N13" s="10" t="s">
+      <c r="N13" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="O13" s="10" t="s">
+      <c r="O13" s="6" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="K14" s="10"/>
-      <c r="N14" s="10"/>
+      <c r="K14" s="6"/>
+      <c r="N14" s="6"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="G15" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="J15" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N15" s="10" t="s">
+      <c r="N15" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="G16" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J16" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="L16" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="N16" s="10" t="s">
+      <c r="N16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="O16" s="10" t="s">
+      <c r="O16" s="6" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="10">
         <v>45757.0</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10" t="s">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="G17" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N17" s="10" t="s">
+      <c r="N17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="O17" s="10" t="s">
+      <c r="O17" s="6" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G18" s="23" t="s">
+      <c r="G18" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N18" s="10" t="s">
+      <c r="N18" s="6" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="20">
         <v>45655.0</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="J19" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="K19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N19" s="10" t="s">
+      <c r="N19" s="6" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="10">
         <v>45769.0</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="K20" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="10" t="s">
+      <c r="N20" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="10">
         <v>45658.0</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="6" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="K22" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="N22" s="10" t="s">
+      <c r="N22" s="6" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="K23" s="10" t="s">
+      <c r="K23" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N23" s="10" t="s">
+      <c r="N23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="O23" s="10" t="s">
+      <c r="O23" s="6" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="26" t="s">
+      <c r="F24" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="G24" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="27" t="s">
+      <c r="H24" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="K24" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N24" s="10" t="s">
+      <c r="N24" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="6" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="10">
         <v>45770.0</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="L26" s="10" t="s">
+      <c r="L26" s="6" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="5">
         <v>2024.0</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="J27" s="10" t="s">
+      <c r="J27" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="K27" s="10" t="s">
+      <c r="K27" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="L27" s="10" t="s">
+      <c r="L27" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="N27" s="10" t="s">
+      <c r="N27" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="10" t="s">
+      <c r="B28" s="24"/>
+      <c r="C28" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D28" s="18"/>
+      <c r="D28" s="14"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="F29" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="K29" s="10" t="s">
+      <c r="K29" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="10" t="s">
+      <c r="N29" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="26">
         <v>45657.0</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="F30" s="32" t="s">
+      <c r="F30" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="G30" s="30" t="s">
+      <c r="G30" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="H30" s="33"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="33"/>
-      <c r="P30" s="33"/>
-      <c r="Q30" s="33"/>
-      <c r="R30" s="33"/>
-      <c r="S30" s="33"/>
-      <c r="T30" s="33"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="28"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="K31" s="10" t="s">
+      <c r="K31" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L31" s="10" t="s">
+      <c r="L31" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="N31" s="10" t="s">
+      <c r="N31" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="B32" s="14">
+      <c r="B32" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="K32" s="10" t="s">
+      <c r="K32" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="10" t="s">
+      <c r="N32" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="B33" s="14">
+      <c r="B33" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="E33" s="34" t="s">
+      <c r="E33" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="G33" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="I33" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="J33" s="10" t="s">
+      <c r="J33" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="K33" s="10" t="s">
+      <c r="K33" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N33" s="10" t="s">
+      <c r="N33" s="6" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="10">
         <v>45763.0</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="E34" s="35" t="s">
+      <c r="E34" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="G34" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="I34" s="10" t="s">
+      <c r="I34" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="J34" s="10" t="s">
+      <c r="J34" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="K34" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="N34" s="10" t="s">
+      <c r="N34" s="6" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="B35" s="14">
+      <c r="B35" s="10">
         <v>45658.0</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="E35" s="35" t="s">
+      <c r="E35" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="G35" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="10" t="s">
+      <c r="K35" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N35" s="10" t="s">
+      <c r="N35" s="6" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B36" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="E36" s="35" t="s">
+      <c r="E36" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="F36" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="G36" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="I36" s="10" t="s">
+      <c r="I36" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="J36" s="10" t="s">
+      <c r="J36" s="6" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="B37" s="14">
+      <c r="B37" s="10">
         <v>45658.0</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="J37" s="10" t="s">
+      <c r="J37" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="K37" s="10" t="s">
+      <c r="K37" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="N37" s="10" t="s">
+      <c r="N37" s="6" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="B38" s="14">
+      <c r="B38" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="G38" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="I38" s="10" t="s">
+      <c r="I38" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="K38" s="10" t="s">
+      <c r="K38" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="L38" s="10" t="s">
+      <c r="L38" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="N38" s="10" t="s">
+      <c r="N38" s="6" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="I39" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="L39" s="10" t="s">
+      <c r="L39" s="6" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="B40" s="14">
+      <c r="B40" s="10">
         <v>44834.0</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="G40" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="J40" s="10" t="s">
+      <c r="J40" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="K40" s="10" t="s">
+      <c r="K40" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="N40" s="10" t="s">
+      <c r="N40" s="6" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="B41" s="14">
+      <c r="B41" s="10">
         <v>45748.0</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="G41" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="I41" s="10" t="s">
+      <c r="I41" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="J41" s="10" t="s">
+      <c r="J41" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="K41" s="10" t="s">
+      <c r="K41" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="L41" s="10" t="s">
+      <c r="L41" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="N41" s="10" t="s">
+      <c r="N41" s="6" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="B42" s="14">
+      <c r="B42" s="10">
         <v>45803.0</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="G42" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="I42" s="10" t="s">
+      <c r="I42" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="J42" s="10" t="s">
+      <c r="J42" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="K42" s="10" t="s">
+      <c r="K42" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="L42" s="10" t="s">
+      <c r="L42" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="N42" s="10" t="s">
+      <c r="N42" s="6" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="B43" s="14">
+      <c r="B43" s="10">
         <v>45473.0</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10" t="s">
+      <c r="F43" s="6"/>
+      <c r="G43" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="I43" s="10" t="s">
+      <c r="I43" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="J43" s="10" t="s">
+      <c r="J43" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="K43" s="10" t="s">
+      <c r="K43" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="L43" s="10" t="s">
+      <c r="L43" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="N43" s="10" t="s">
+      <c r="N43" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="O43" s="10" t="s">
+      <c r="O43" s="6" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="B44" s="14">
+      <c r="B44" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="G44" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I44" s="10" t="s">
+      <c r="I44" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="J44" s="10" t="s">
+      <c r="J44" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="O44" s="10"/>
+      <c r="O44" s="6"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="B45" s="14">
+      <c r="B45" s="10">
         <v>45535.0</v>
       </c>
-      <c r="C45" s="36" t="s">
+      <c r="C45" s="31" t="s">
         <v>339</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="I45" s="10" t="s">
+      <c r="I45" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="J45" s="10" t="s">
+      <c r="J45" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="K45" s="10" t="s">
+      <c r="K45" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="10" t="s">
+      <c r="L45" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="N45" s="10" t="s">
+      <c r="N45" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="O45" s="10"/>
+      <c r="O45" s="6"/>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="D46" s="18"/>
+      <c r="D46" s="14"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="10">
         <v>45565.0</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="G47" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="I47" s="10" t="s">
+      <c r="I47" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="J47" s="10" t="s">
+      <c r="J47" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="K47" s="10" t="s">
+      <c r="K47" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="L47" s="10" t="s">
+      <c r="L47" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="N47" s="10" t="s">
+      <c r="N47" s="6" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="B48" s="14">
+      <c r="B48" s="10">
         <v>45658.0</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="E48" s="10" t="s">
+      <c r="E48" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="F48" s="10" t="s">
+      <c r="F48" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="G48" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="J48" s="10" t="s">
+      <c r="J48" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="K48" s="10" t="s">
+      <c r="K48" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="N48" s="10" t="s">
+      <c r="N48" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="O48" s="10" t="s">
+      <c r="O48" s="6" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="B49" s="14">
+      <c r="B49" s="10">
         <v>45473.0</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="G49" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="I49" s="10" t="s">
+      <c r="I49" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="K49" s="10" t="s">
+      <c r="K49" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="N49" s="10" t="s">
+      <c r="N49" s="6" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="B50" s="14">
+      <c r="B50" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="F50" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G50" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="I50" s="10" t="s">
+      <c r="I50" s="6" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="10">
         <v>45291.0</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F51" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="G51" s="6" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="10">
         <v>45657.0</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="F52" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="G52" s="10" t="s">
+      <c r="G52" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="I52" s="10" t="s">
+      <c r="I52" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="J52" s="10" t="s">
+      <c r="J52" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="K52" s="10" t="s">
+      <c r="K52" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="N52" s="10" t="s">
+      <c r="N52" s="6" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="29"/>
+      <c r="B53" s="24"/>
     </row>
     <row r="54">
-      <c r="B54" s="29"/>
+      <c r="B54" s="24"/>
     </row>
     <row r="55">
-      <c r="B55" s="29"/>
+      <c r="B55" s="24"/>
     </row>
     <row r="56">
-      <c r="B56" s="29"/>
+      <c r="B56" s="24"/>
     </row>
     <row r="57">
-      <c r="B57" s="29"/>
+      <c r="B57" s="24"/>
     </row>
     <row r="58">
-      <c r="B58" s="29"/>
+      <c r="B58" s="24"/>
     </row>
     <row r="59">
-      <c r="B59" s="29"/>
+      <c r="B59" s="24"/>
     </row>
     <row r="60">
-      <c r="B60" s="29"/>
+      <c r="B60" s="24"/>
     </row>
     <row r="61">
-      <c r="B61" s="29"/>
+      <c r="B61" s="24"/>
     </row>
     <row r="62">
-      <c r="B62" s="29"/>
+      <c r="B62" s="24"/>
     </row>
     <row r="63">
-      <c r="B63" s="29"/>
+      <c r="B63" s="24"/>
     </row>
     <row r="64">
-      <c r="B64" s="29"/>
+      <c r="B64" s="24"/>
     </row>
     <row r="65">
-      <c r="B65" s="29"/>
+      <c r="B65" s="24"/>
     </row>
     <row r="66">
-      <c r="B66" s="29"/>
+      <c r="B66" s="24"/>
     </row>
     <row r="67">
-      <c r="B67" s="29"/>
+      <c r="B67" s="24"/>
     </row>
     <row r="68">
-      <c r="B68" s="29"/>
+      <c r="B68" s="24"/>
     </row>
     <row r="69">
-      <c r="B69" s="29"/>
+      <c r="B69" s="24"/>
     </row>
     <row r="70">
-      <c r="B70" s="29"/>
+      <c r="B70" s="24"/>
     </row>
     <row r="71">
-      <c r="B71" s="29"/>
+      <c r="B71" s="24"/>
     </row>
     <row r="72">
-      <c r="B72" s="29"/>
+      <c r="B72" s="24"/>
     </row>
     <row r="73">
-      <c r="B73" s="29"/>
+      <c r="B73" s="24"/>
     </row>
     <row r="74">
-      <c r="B74" s="29"/>
+      <c r="B74" s="24"/>
     </row>
     <row r="75">
-      <c r="B75" s="29"/>
+      <c r="B75" s="24"/>
     </row>
     <row r="76">
-      <c r="B76" s="29"/>
+      <c r="B76" s="24"/>
     </row>
     <row r="77">
-      <c r="B77" s="29"/>
+      <c r="B77" s="24"/>
     </row>
     <row r="78">
-      <c r="B78" s="29"/>
+      <c r="B78" s="24"/>
     </row>
     <row r="79">
-      <c r="B79" s="29"/>
+      <c r="B79" s="24"/>
     </row>
     <row r="80">
-      <c r="B80" s="29"/>
+      <c r="B80" s="24"/>
     </row>
     <row r="81">
-      <c r="B81" s="29"/>
+      <c r="B81" s="24"/>
     </row>
     <row r="82">
-      <c r="B82" s="29"/>
+      <c r="B82" s="24"/>
     </row>
     <row r="83">
-      <c r="B83" s="29"/>
+      <c r="B83" s="24"/>
     </row>
     <row r="84">
-      <c r="B84" s="29"/>
+      <c r="B84" s="24"/>
     </row>
     <row r="85">
-      <c r="B85" s="29"/>
+      <c r="B85" s="24"/>
     </row>
     <row r="86">
-      <c r="B86" s="29"/>
+      <c r="B86" s="24"/>
     </row>
     <row r="87">
-      <c r="B87" s="29"/>
+      <c r="B87" s="24"/>
     </row>
     <row r="88">
-      <c r="B88" s="29"/>
+      <c r="B88" s="24"/>
     </row>
     <row r="89">
-      <c r="B89" s="29"/>
+      <c r="B89" s="24"/>
     </row>
     <row r="90">
-      <c r="B90" s="29"/>
+      <c r="B90" s="24"/>
     </row>
     <row r="91">
-      <c r="B91" s="29"/>
+      <c r="B91" s="24"/>
     </row>
     <row r="92">
-      <c r="B92" s="29"/>
+      <c r="B92" s="24"/>
     </row>
     <row r="93">
-      <c r="B93" s="29"/>
+      <c r="B93" s="24"/>
     </row>
     <row r="94">
-      <c r="B94" s="29"/>
+      <c r="B94" s="24"/>
     </row>
     <row r="95">
-      <c r="B95" s="29"/>
+      <c r="B95" s="24"/>
     </row>
     <row r="96">
-      <c r="B96" s="29"/>
+      <c r="B96" s="24"/>
     </row>
     <row r="97">
-      <c r="B97" s="29"/>
+      <c r="B97" s="24"/>
     </row>
     <row r="98">
-      <c r="B98" s="29"/>
+      <c r="B98" s="24"/>
     </row>
     <row r="99">
-      <c r="B99" s="29"/>
+      <c r="B99" s="24"/>
     </row>
     <row r="100">
-      <c r="B100" s="29"/>
+      <c r="B100" s="24"/>
     </row>
     <row r="101">
-      <c r="B101" s="29"/>
+      <c r="B101" s="24"/>
     </row>
     <row r="102">
-      <c r="B102" s="29"/>
+      <c r="B102" s="24"/>
     </row>
     <row r="103">
-      <c r="B103" s="29"/>
+      <c r="B103" s="24"/>
     </row>
     <row r="104">
-      <c r="B104" s="29"/>
+      <c r="B104" s="24"/>
     </row>
     <row r="105">
-      <c r="B105" s="29"/>
+      <c r="B105" s="24"/>
     </row>
     <row r="106">
-      <c r="B106" s="29"/>
+      <c r="B106" s="24"/>
     </row>
     <row r="107">
-      <c r="B107" s="29"/>
+      <c r="B107" s="24"/>
     </row>
     <row r="108">
-      <c r="B108" s="29"/>
+      <c r="B108" s="24"/>
     </row>
     <row r="109">
-      <c r="B109" s="29"/>
+      <c r="B109" s="24"/>
     </row>
     <row r="110">
-      <c r="B110" s="29"/>
+      <c r="B110" s="24"/>
     </row>
     <row r="111">
-      <c r="B111" s="29"/>
+      <c r="B111" s="24"/>
     </row>
     <row r="112">
-      <c r="B112" s="29"/>
+      <c r="B112" s="24"/>
     </row>
     <row r="113">
-      <c r="B113" s="29"/>
+      <c r="B113" s="24"/>
     </row>
     <row r="114">
-      <c r="B114" s="29"/>
+      <c r="B114" s="24"/>
     </row>
     <row r="115">
-      <c r="B115" s="29"/>
+      <c r="B115" s="24"/>
     </row>
     <row r="116">
-      <c r="B116" s="29"/>
+      <c r="B116" s="24"/>
     </row>
     <row r="117">
-      <c r="B117" s="29"/>
+      <c r="B117" s="24"/>
     </row>
     <row r="118">
-      <c r="B118" s="29"/>
+      <c r="B118" s="24"/>
     </row>
     <row r="119">
-      <c r="B119" s="29"/>
+      <c r="B119" s="24"/>
     </row>
     <row r="120">
-      <c r="B120" s="29"/>
+      <c r="B120" s="24"/>
     </row>
     <row r="121">
-      <c r="B121" s="29"/>
+      <c r="B121" s="24"/>
     </row>
     <row r="122">
-      <c r="B122" s="29"/>
+      <c r="B122" s="24"/>
     </row>
     <row r="123">
-      <c r="B123" s="29"/>
+      <c r="B123" s="24"/>
     </row>
     <row r="124">
-      <c r="B124" s="29"/>
+      <c r="B124" s="24"/>
     </row>
     <row r="125">
-      <c r="B125" s="29"/>
+      <c r="B125" s="24"/>
     </row>
     <row r="126">
-      <c r="B126" s="29"/>
+      <c r="B126" s="24"/>
     </row>
     <row r="127">
-      <c r="B127" s="29"/>
+      <c r="B127" s="24"/>
     </row>
     <row r="128">
-      <c r="B128" s="29"/>
+      <c r="B128" s="24"/>
     </row>
     <row r="129">
-      <c r="B129" s="29"/>
+      <c r="B129" s="24"/>
     </row>
     <row r="130">
-      <c r="B130" s="29"/>
+      <c r="B130" s="24"/>
     </row>
     <row r="131">
-      <c r="B131" s="29"/>
+      <c r="B131" s="24"/>
     </row>
     <row r="132">
-      <c r="B132" s="29"/>
+      <c r="B132" s="24"/>
     </row>
     <row r="133">
-      <c r="B133" s="29"/>
+      <c r="B133" s="24"/>
     </row>
     <row r="134">
-      <c r="B134" s="29"/>
+      <c r="B134" s="24"/>
     </row>
     <row r="135">
-      <c r="B135" s="29"/>
+      <c r="B135" s="24"/>
     </row>
     <row r="136">
-      <c r="B136" s="29"/>
+      <c r="B136" s="24"/>
     </row>
     <row r="137">
-      <c r="B137" s="29"/>
+      <c r="B137" s="24"/>
     </row>
     <row r="138">
-      <c r="B138" s="29"/>
+      <c r="B138" s="24"/>
     </row>
     <row r="139">
-      <c r="B139" s="29"/>
+      <c r="B139" s="24"/>
     </row>
     <row r="140">
-      <c r="B140" s="29"/>
+      <c r="B140" s="24"/>
     </row>
     <row r="141">
-      <c r="B141" s="29"/>
+      <c r="B141" s="24"/>
     </row>
     <row r="142">
-      <c r="B142" s="29"/>
+      <c r="B142" s="24"/>
     </row>
     <row r="143">
-      <c r="B143" s="29"/>
+      <c r="B143" s="24"/>
     </row>
     <row r="144">
-      <c r="B144" s="29"/>
+      <c r="B144" s="24"/>
     </row>
     <row r="145">
-      <c r="B145" s="29"/>
+      <c r="B145" s="24"/>
     </row>
     <row r="146">
-      <c r="B146" s="29"/>
+      <c r="B146" s="24"/>
     </row>
     <row r="147">
-      <c r="B147" s="29"/>
+      <c r="B147" s="24"/>
     </row>
     <row r="148">
-      <c r="B148" s="29"/>
+      <c r="B148" s="24"/>
     </row>
     <row r="149">
-      <c r="B149" s="29"/>
+      <c r="B149" s="24"/>
     </row>
     <row r="150">
-      <c r="B150" s="29"/>
+      <c r="B150" s="24"/>
     </row>
     <row r="151">
-      <c r="B151" s="29"/>
+      <c r="B151" s="24"/>
     </row>
     <row r="152">
-      <c r="B152" s="29"/>
+      <c r="B152" s="24"/>
     </row>
     <row r="153">
-      <c r="B153" s="29"/>
+      <c r="B153" s="24"/>
     </row>
     <row r="154">
-      <c r="B154" s="29"/>
+      <c r="B154" s="24"/>
     </row>
     <row r="155">
-      <c r="B155" s="29"/>
+      <c r="B155" s="24"/>
     </row>
     <row r="156">
-      <c r="B156" s="29"/>
+      <c r="B156" s="24"/>
     </row>
     <row r="157">
-      <c r="B157" s="29"/>
+      <c r="B157" s="24"/>
     </row>
     <row r="158">
-      <c r="B158" s="29"/>
+      <c r="B158" s="24"/>
     </row>
     <row r="159">
-      <c r="B159" s="29"/>
+      <c r="B159" s="24"/>
     </row>
     <row r="160">
-      <c r="B160" s="29"/>
+      <c r="B160" s="24"/>
     </row>
     <row r="161">
-      <c r="B161" s="29"/>
+      <c r="B161" s="24"/>
     </row>
     <row r="162">
-      <c r="B162" s="29"/>
+      <c r="B162" s="24"/>
     </row>
     <row r="163">
-      <c r="B163" s="29"/>
+      <c r="B163" s="24"/>
     </row>
     <row r="164">
-      <c r="B164" s="29"/>
+      <c r="B164" s="24"/>
     </row>
     <row r="165">
-      <c r="B165" s="29"/>
+      <c r="B165" s="24"/>
     </row>
     <row r="166">
-      <c r="B166" s="29"/>
+      <c r="B166" s="24"/>
     </row>
     <row r="167">
-      <c r="B167" s="29"/>
+      <c r="B167" s="24"/>
     </row>
     <row r="168">
-      <c r="B168" s="29"/>
+      <c r="B168" s="24"/>
     </row>
     <row r="169">
-      <c r="B169" s="29"/>
+      <c r="B169" s="24"/>
     </row>
     <row r="170">
-      <c r="B170" s="29"/>
+      <c r="B170" s="24"/>
     </row>
     <row r="171">
-      <c r="B171" s="29"/>
+      <c r="B171" s="24"/>
     </row>
     <row r="172">
-      <c r="B172" s="29"/>
+      <c r="B172" s="24"/>
     </row>
     <row r="173">
-      <c r="B173" s="29"/>
+      <c r="B173" s="24"/>
     </row>
     <row r="174">
-      <c r="B174" s="29"/>
+      <c r="B174" s="24"/>
     </row>
     <row r="175">
-      <c r="B175" s="29"/>
+      <c r="B175" s="24"/>
     </row>
     <row r="176">
-      <c r="B176" s="29"/>
+      <c r="B176" s="24"/>
     </row>
     <row r="177">
-      <c r="B177" s="29"/>
+      <c r="B177" s="24"/>
     </row>
     <row r="178">
-      <c r="B178" s="29"/>
+      <c r="B178" s="24"/>
     </row>
     <row r="179">
-      <c r="B179" s="29"/>
+      <c r="B179" s="24"/>
     </row>
     <row r="180">
-      <c r="B180" s="29"/>
+      <c r="B180" s="24"/>
     </row>
     <row r="181">
-      <c r="B181" s="29"/>
+      <c r="B181" s="24"/>
     </row>
     <row r="182">
-      <c r="B182" s="29"/>
+      <c r="B182" s="24"/>
     </row>
     <row r="183">
-      <c r="B183" s="29"/>
+      <c r="B183" s="24"/>
     </row>
     <row r="184">
-      <c r="B184" s="29"/>
+      <c r="B184" s="24"/>
     </row>
     <row r="185">
-      <c r="B185" s="29"/>
+      <c r="B185" s="24"/>
     </row>
     <row r="186">
-      <c r="B186" s="29"/>
+      <c r="B186" s="24"/>
     </row>
     <row r="187">
-      <c r="B187" s="29"/>
+      <c r="B187" s="24"/>
     </row>
     <row r="188">
-      <c r="B188" s="29"/>
+      <c r="B188" s="24"/>
     </row>
     <row r="189">
-      <c r="B189" s="29"/>
+      <c r="B189" s="24"/>
     </row>
     <row r="190">
-      <c r="B190" s="29"/>
+      <c r="B190" s="24"/>
     </row>
     <row r="191">
-      <c r="B191" s="29"/>
+      <c r="B191" s="24"/>
     </row>
     <row r="192">
-      <c r="B192" s="29"/>
+      <c r="B192" s="24"/>
     </row>
     <row r="193">
-      <c r="B193" s="29"/>
+      <c r="B193" s="24"/>
     </row>
     <row r="194">
-      <c r="B194" s="29"/>
+      <c r="B194" s="24"/>
     </row>
     <row r="195">
-      <c r="B195" s="29"/>
+      <c r="B195" s="24"/>
     </row>
     <row r="196">
-      <c r="B196" s="29"/>
+      <c r="B196" s="24"/>
     </row>
     <row r="197">
-      <c r="B197" s="29"/>
+      <c r="B197" s="24"/>
     </row>
     <row r="198">
-      <c r="B198" s="29"/>
+      <c r="B198" s="24"/>
     </row>
     <row r="199">
-      <c r="B199" s="29"/>
+      <c r="B199" s="24"/>
     </row>
     <row r="200">
-      <c r="B200" s="29"/>
+      <c r="B200" s="24"/>
     </row>
     <row r="201">
-      <c r="B201" s="29"/>
+      <c r="B201" s="24"/>
     </row>
     <row r="202">
-      <c r="B202" s="29"/>
+      <c r="B202" s="24"/>
     </row>
     <row r="203">
-      <c r="B203" s="29"/>
+      <c r="B203" s="24"/>
     </row>
     <row r="204">
-      <c r="B204" s="29"/>
+      <c r="B204" s="24"/>
     </row>
     <row r="205">
-      <c r="B205" s="29"/>
+      <c r="B205" s="24"/>
     </row>
     <row r="206">
-      <c r="B206" s="29"/>
+      <c r="B206" s="24"/>
     </row>
     <row r="207">
-      <c r="B207" s="29"/>
+      <c r="B207" s="24"/>
     </row>
     <row r="208">
-      <c r="B208" s="29"/>
+      <c r="B208" s="24"/>
     </row>
     <row r="209">
-      <c r="B209" s="29"/>
+      <c r="B209" s="24"/>
     </row>
     <row r="210">
-      <c r="B210" s="29"/>
+      <c r="B210" s="24"/>
     </row>
     <row r="211">
-      <c r="B211" s="29"/>
+      <c r="B211" s="24"/>
     </row>
     <row r="212">
-      <c r="B212" s="29"/>
+      <c r="B212" s="24"/>
     </row>
     <row r="213">
-      <c r="B213" s="29"/>
+      <c r="B213" s="24"/>
     </row>
     <row r="214">
-      <c r="B214" s="29"/>
+      <c r="B214" s="24"/>
     </row>
     <row r="215">
-      <c r="B215" s="29"/>
+      <c r="B215" s="24"/>
     </row>
     <row r="216">
-      <c r="B216" s="29"/>
+      <c r="B216" s="24"/>
     </row>
     <row r="217">
-      <c r="B217" s="29"/>
+      <c r="B217" s="24"/>
     </row>
     <row r="218">
-      <c r="B218" s="29"/>
+      <c r="B218" s="24"/>
     </row>
     <row r="219">
-      <c r="B219" s="29"/>
+      <c r="B219" s="24"/>
     </row>
     <row r="220">
-      <c r="B220" s="29"/>
+      <c r="B220" s="24"/>
     </row>
     <row r="221">
-      <c r="B221" s="29"/>
+      <c r="B221" s="24"/>
     </row>
     <row r="222">
-      <c r="B222" s="29"/>
+      <c r="B222" s="24"/>
     </row>
     <row r="223">
-      <c r="B223" s="29"/>
+      <c r="B223" s="24"/>
     </row>
     <row r="224">
-      <c r="B224" s="29"/>
+      <c r="B224" s="24"/>
     </row>
     <row r="225">
-      <c r="B225" s="29"/>
+      <c r="B225" s="24"/>
     </row>
     <row r="226">
-      <c r="B226" s="29"/>
+      <c r="B226" s="24"/>
     </row>
     <row r="227">
-      <c r="B227" s="29"/>
+      <c r="B227" s="24"/>
     </row>
     <row r="228">
-      <c r="B228" s="29"/>
+      <c r="B228" s="24"/>
     </row>
     <row r="229">
-      <c r="B229" s="29"/>
+      <c r="B229" s="24"/>
     </row>
     <row r="230">
-      <c r="B230" s="29"/>
+      <c r="B230" s="24"/>
     </row>
     <row r="231">
-      <c r="B231" s="29"/>
+      <c r="B231" s="24"/>
     </row>
     <row r="232">
-      <c r="B232" s="29"/>
+      <c r="B232" s="24"/>
     </row>
     <row r="233">
-      <c r="B233" s="29"/>
+      <c r="B233" s="24"/>
     </row>
     <row r="234">
-      <c r="B234" s="29"/>
+      <c r="B234" s="24"/>
     </row>
     <row r="235">
-      <c r="B235" s="29"/>
+      <c r="B235" s="24"/>
     </row>
     <row r="236">
-      <c r="B236" s="29"/>
+      <c r="B236" s="24"/>
     </row>
     <row r="237">
-      <c r="B237" s="29"/>
+      <c r="B237" s="24"/>
     </row>
     <row r="238">
-      <c r="B238" s="29"/>
+      <c r="B238" s="24"/>
     </row>
     <row r="239">
-      <c r="B239" s="29"/>
+      <c r="B239" s="24"/>
     </row>
     <row r="240">
-      <c r="B240" s="29"/>
+      <c r="B240" s="24"/>
     </row>
     <row r="241">
-      <c r="B241" s="29"/>
+      <c r="B241" s="24"/>
     </row>
     <row r="242">
-      <c r="B242" s="29"/>
+      <c r="B242" s="24"/>
     </row>
     <row r="243">
-      <c r="B243" s="29"/>
+      <c r="B243" s="24"/>
     </row>
     <row r="244">
-      <c r="B244" s="29"/>
+      <c r="B244" s="24"/>
     </row>
     <row r="245">
-      <c r="B245" s="29"/>
+      <c r="B245" s="24"/>
     </row>
     <row r="246">
-      <c r="B246" s="29"/>
+      <c r="B246" s="24"/>
     </row>
     <row r="247">
-      <c r="B247" s="29"/>
+      <c r="B247" s="24"/>
     </row>
     <row r="248">
-      <c r="B248" s="29"/>
+      <c r="B248" s="24"/>
     </row>
     <row r="249">
-      <c r="B249" s="29"/>
+      <c r="B249" s="24"/>
     </row>
     <row r="250">
-      <c r="B250" s="29"/>
+      <c r="B250" s="24"/>
     </row>
     <row r="251">
-      <c r="B251" s="29"/>
+      <c r="B251" s="24"/>
     </row>
     <row r="252">
-      <c r="B252" s="29"/>
+      <c r="B252" s="24"/>
     </row>
     <row r="253">
-      <c r="B253" s="29"/>
+      <c r="B253" s="24"/>
     </row>
     <row r="254">
-      <c r="B254" s="29"/>
+      <c r="B254" s="24"/>
     </row>
     <row r="255">
-      <c r="B255" s="29"/>
+      <c r="B255" s="24"/>
     </row>
     <row r="256">
-      <c r="B256" s="29"/>
+      <c r="B256" s="24"/>
     </row>
     <row r="257">
-      <c r="B257" s="29"/>
+      <c r="B257" s="24"/>
     </row>
     <row r="258">
-      <c r="B258" s="29"/>
+      <c r="B258" s="24"/>
     </row>
     <row r="259">
-      <c r="B259" s="29"/>
+      <c r="B259" s="24"/>
     </row>
     <row r="260">
-      <c r="B260" s="29"/>
+      <c r="B260" s="24"/>
     </row>
     <row r="261">
-      <c r="B261" s="29"/>
+      <c r="B261" s="24"/>
     </row>
     <row r="262">
-      <c r="B262" s="29"/>
+      <c r="B262" s="24"/>
     </row>
     <row r="263">
-      <c r="B263" s="29"/>
+      <c r="B263" s="24"/>
     </row>
     <row r="264">
-      <c r="B264" s="29"/>
+      <c r="B264" s="24"/>
     </row>
     <row r="265">
-      <c r="B265" s="29"/>
+      <c r="B265" s="24"/>
     </row>
     <row r="266">
-      <c r="B266" s="29"/>
+      <c r="B266" s="24"/>
     </row>
     <row r="267">
-      <c r="B267" s="29"/>
+      <c r="B267" s="24"/>
     </row>
     <row r="268">
-      <c r="B268" s="29"/>
+      <c r="B268" s="24"/>
     </row>
     <row r="269">
-      <c r="B269" s="29"/>
+      <c r="B269" s="24"/>
     </row>
     <row r="270">
-      <c r="B270" s="29"/>
+      <c r="B270" s="24"/>
     </row>
     <row r="271">
-      <c r="B271" s="29"/>
+      <c r="B271" s="24"/>
     </row>
     <row r="272">
-      <c r="B272" s="29"/>
+      <c r="B272" s="24"/>
     </row>
     <row r="273">
-      <c r="B273" s="29"/>
+      <c r="B273" s="24"/>
     </row>
     <row r="274">
-      <c r="B274" s="29"/>
+      <c r="B274" s="24"/>
     </row>
     <row r="275">
-      <c r="B275" s="29"/>
+      <c r="B275" s="24"/>
     </row>
     <row r="276">
-      <c r="B276" s="29"/>
+      <c r="B276" s="24"/>
     </row>
     <row r="277">
-      <c r="B277" s="29"/>
+      <c r="B277" s="24"/>
     </row>
     <row r="278">
-      <c r="B278" s="29"/>
+      <c r="B278" s="24"/>
     </row>
     <row r="279">
-      <c r="B279" s="29"/>
+      <c r="B279" s="24"/>
     </row>
     <row r="280">
-      <c r="B280" s="29"/>
+      <c r="B280" s="24"/>
     </row>
     <row r="281">
-      <c r="B281" s="29"/>
+      <c r="B281" s="24"/>
     </row>
     <row r="282">
-      <c r="B282" s="29"/>
+      <c r="B282" s="24"/>
     </row>
     <row r="283">
-      <c r="B283" s="29"/>
+      <c r="B283" s="24"/>
     </row>
     <row r="284">
-      <c r="B284" s="29"/>
+      <c r="B284" s="24"/>
     </row>
     <row r="285">
-      <c r="B285" s="29"/>
+      <c r="B285" s="24"/>
     </row>
     <row r="286">
-      <c r="B286" s="29"/>
+      <c r="B286" s="24"/>
     </row>
     <row r="287">
-      <c r="B287" s="29"/>
+      <c r="B287" s="24"/>
     </row>
     <row r="288">
-      <c r="B288" s="29"/>
+      <c r="B288" s="24"/>
     </row>
     <row r="289">
-      <c r="B289" s="29"/>
+      <c r="B289" s="24"/>
     </row>
     <row r="290">
-      <c r="B290" s="29"/>
+      <c r="B290" s="24"/>
     </row>
     <row r="291">
-      <c r="B291" s="29"/>
+      <c r="B291" s="24"/>
     </row>
     <row r="292">
-      <c r="B292" s="29"/>
+      <c r="B292" s="24"/>
     </row>
     <row r="293">
-      <c r="B293" s="29"/>
+      <c r="B293" s="24"/>
     </row>
     <row r="294">
-      <c r="B294" s="29"/>
+      <c r="B294" s="24"/>
     </row>
     <row r="295">
-      <c r="B295" s="29"/>
+      <c r="B295" s="24"/>
     </row>
     <row r="296">
-      <c r="B296" s="29"/>
+      <c r="B296" s="24"/>
     </row>
     <row r="297">
-      <c r="B297" s="29"/>
+      <c r="B297" s="24"/>
     </row>
     <row r="298">
-      <c r="B298" s="29"/>
+      <c r="B298" s="24"/>
     </row>
     <row r="299">
-      <c r="B299" s="29"/>
+      <c r="B299" s="24"/>
     </row>
     <row r="300">
-      <c r="B300" s="29"/>
+      <c r="B300" s="24"/>
     </row>
     <row r="301">
-      <c r="B301" s="29"/>
+      <c r="B301" s="24"/>
     </row>
     <row r="302">
-      <c r="B302" s="29"/>
+      <c r="B302" s="24"/>
     </row>
     <row r="303">
-      <c r="B303" s="29"/>
+      <c r="B303" s="24"/>
     </row>
     <row r="304">
-      <c r="B304" s="29"/>
+      <c r="B304" s="24"/>
     </row>
     <row r="305">
-      <c r="B305" s="29"/>
+      <c r="B305" s="24"/>
     </row>
     <row r="306">
-      <c r="B306" s="29"/>
+      <c r="B306" s="24"/>
     </row>
     <row r="307">
-      <c r="B307" s="29"/>
+      <c r="B307" s="24"/>
     </row>
     <row r="308">
-      <c r="B308" s="29"/>
+      <c r="B308" s="24"/>
     </row>
     <row r="309">
-      <c r="B309" s="29"/>
+      <c r="B309" s="24"/>
     </row>
     <row r="310">
-      <c r="B310" s="29"/>
+      <c r="B310" s="24"/>
     </row>
     <row r="311">
-      <c r="B311" s="29"/>
+      <c r="B311" s="24"/>
     </row>
     <row r="312">
-      <c r="B312" s="29"/>
+      <c r="B312" s="24"/>
     </row>
     <row r="313">
-      <c r="B313" s="29"/>
+      <c r="B313" s="24"/>
     </row>
     <row r="314">
-      <c r="B314" s="29"/>
+      <c r="B314" s="24"/>
     </row>
     <row r="315">
-      <c r="B315" s="29"/>
+      <c r="B315" s="24"/>
     </row>
     <row r="316">
-      <c r="B316" s="29"/>
+      <c r="B316" s="24"/>
     </row>
     <row r="317">
-      <c r="B317" s="29"/>
+      <c r="B317" s="24"/>
     </row>
     <row r="318">
-      <c r="B318" s="29"/>
+      <c r="B318" s="24"/>
     </row>
     <row r="319">
-      <c r="B319" s="29"/>
+      <c r="B319" s="24"/>
     </row>
     <row r="320">
-      <c r="B320" s="29"/>
+      <c r="B320" s="24"/>
     </row>
     <row r="321">
-      <c r="B321" s="29"/>
+      <c r="B321" s="24"/>
     </row>
     <row r="322">
-      <c r="B322" s="29"/>
+      <c r="B322" s="24"/>
     </row>
     <row r="323">
-      <c r="B323" s="29"/>
+      <c r="B323" s="24"/>
     </row>
     <row r="324">
-      <c r="B324" s="29"/>
+      <c r="B324" s="24"/>
     </row>
     <row r="325">
-      <c r="B325" s="29"/>
+      <c r="B325" s="24"/>
     </row>
     <row r="326">
-      <c r="B326" s="29"/>
+      <c r="B326" s="24"/>
     </row>
     <row r="327">
-      <c r="B327" s="29"/>
+      <c r="B327" s="24"/>
     </row>
     <row r="328">
-      <c r="B328" s="29"/>
+      <c r="B328" s="24"/>
     </row>
     <row r="329">
-      <c r="B329" s="29"/>
+      <c r="B329" s="24"/>
     </row>
     <row r="330">
-      <c r="B330" s="29"/>
+      <c r="B330" s="24"/>
     </row>
     <row r="331">
-      <c r="B331" s="29"/>
+      <c r="B331" s="24"/>
     </row>
     <row r="332">
-      <c r="B332" s="29"/>
+      <c r="B332" s="24"/>
     </row>
     <row r="333">
-      <c r="B333" s="29"/>
+      <c r="B333" s="24"/>
     </row>
     <row r="334">
-      <c r="B334" s="29"/>
+      <c r="B334" s="24"/>
     </row>
     <row r="335">
-      <c r="B335" s="29"/>
+      <c r="B335" s="24"/>
     </row>
     <row r="336">
-      <c r="B336" s="29"/>
+      <c r="B336" s="24"/>
     </row>
     <row r="337">
-      <c r="B337" s="29"/>
+      <c r="B337" s="24"/>
     </row>
     <row r="338">
-      <c r="B338" s="29"/>
+      <c r="B338" s="24"/>
     </row>
     <row r="339">
-      <c r="B339" s="29"/>
+      <c r="B339" s="24"/>
     </row>
     <row r="340">
-      <c r="B340" s="29"/>
+      <c r="B340" s="24"/>
     </row>
     <row r="341">
-      <c r="B341" s="29"/>
+      <c r="B341" s="24"/>
     </row>
     <row r="342">
-      <c r="B342" s="29"/>
+      <c r="B342" s="24"/>
     </row>
     <row r="343">
-      <c r="B343" s="29"/>
+      <c r="B343" s="24"/>
     </row>
     <row r="344">
-      <c r="B344" s="29"/>
+      <c r="B344" s="24"/>
     </row>
     <row r="345">
-      <c r="B345" s="29"/>
+      <c r="B345" s="24"/>
     </row>
     <row r="346">
-      <c r="B346" s="29"/>
+      <c r="B346" s="24"/>
     </row>
     <row r="347">
-      <c r="B347" s="29"/>
+      <c r="B347" s="24"/>
     </row>
     <row r="348">
-      <c r="B348" s="29"/>
+      <c r="B348" s="24"/>
     </row>
     <row r="349">
-      <c r="B349" s="29"/>
+      <c r="B349" s="24"/>
     </row>
     <row r="350">
-      <c r="B350" s="29"/>
+      <c r="B350" s="24"/>
     </row>
     <row r="351">
-      <c r="B351" s="29"/>
+      <c r="B351" s="24"/>
     </row>
     <row r="352">
-      <c r="B352" s="29"/>
+      <c r="B352" s="24"/>
     </row>
     <row r="353">
-      <c r="B353" s="29"/>
+      <c r="B353" s="24"/>
     </row>
     <row r="354">
-      <c r="B354" s="29"/>
+      <c r="B354" s="24"/>
     </row>
     <row r="355">
-      <c r="B355" s="29"/>
+      <c r="B355" s="24"/>
     </row>
     <row r="356">
-      <c r="B356" s="29"/>
+      <c r="B356" s="24"/>
     </row>
     <row r="357">
-      <c r="B357" s="29"/>
+      <c r="B357" s="24"/>
     </row>
     <row r="358">
-      <c r="B358" s="29"/>
+      <c r="B358" s="24"/>
     </row>
     <row r="359">
-      <c r="B359" s="29"/>
+      <c r="B359" s="24"/>
     </row>
     <row r="360">
-      <c r="B360" s="29"/>
+      <c r="B360" s="24"/>
     </row>
     <row r="361">
-      <c r="B361" s="29"/>
+      <c r="B361" s="24"/>
     </row>
     <row r="362">
-      <c r="B362" s="29"/>
+      <c r="B362" s="24"/>
     </row>
     <row r="363">
-      <c r="B363" s="29"/>
+      <c r="B363" s="24"/>
     </row>
     <row r="364">
-      <c r="B364" s="29"/>
+      <c r="B364" s="24"/>
     </row>
     <row r="365">
-      <c r="B365" s="29"/>
+      <c r="B365" s="24"/>
     </row>
     <row r="366">
-      <c r="B366" s="29"/>
+      <c r="B366" s="24"/>
     </row>
     <row r="367">
-      <c r="B367" s="29"/>
+      <c r="B367" s="24"/>
     </row>
     <row r="368">
-      <c r="B368" s="29"/>
+      <c r="B368" s="24"/>
     </row>
     <row r="369">
-      <c r="B369" s="29"/>
+      <c r="B369" s="24"/>
     </row>
     <row r="370">
-      <c r="B370" s="29"/>
+      <c r="B370" s="24"/>
     </row>
     <row r="371">
-      <c r="B371" s="29"/>
+      <c r="B371" s="24"/>
     </row>
     <row r="372">
-      <c r="B372" s="29"/>
+      <c r="B372" s="24"/>
     </row>
     <row r="373">
-      <c r="B373" s="29"/>
+      <c r="B373" s="24"/>
     </row>
     <row r="374">
-      <c r="B374" s="29"/>
+      <c r="B374" s="24"/>
     </row>
     <row r="375">
-      <c r="B375" s="29"/>
+      <c r="B375" s="24"/>
     </row>
     <row r="376">
-      <c r="B376" s="29"/>
+      <c r="B376" s="24"/>
     </row>
     <row r="377">
-      <c r="B377" s="29"/>
+      <c r="B377" s="24"/>
     </row>
     <row r="378">
-      <c r="B378" s="29"/>
+      <c r="B378" s="24"/>
     </row>
     <row r="379">
-      <c r="B379" s="29"/>
+      <c r="B379" s="24"/>
     </row>
     <row r="380">
-      <c r="B380" s="29"/>
+      <c r="B380" s="24"/>
     </row>
     <row r="381">
-      <c r="B381" s="29"/>
+      <c r="B381" s="24"/>
     </row>
     <row r="382">
-      <c r="B382" s="29"/>
+      <c r="B382" s="24"/>
     </row>
     <row r="383">
-      <c r="B383" s="29"/>
+      <c r="B383" s="24"/>
     </row>
     <row r="384">
-      <c r="B384" s="29"/>
+      <c r="B384" s="24"/>
     </row>
     <row r="385">
-      <c r="B385" s="29"/>
+      <c r="B385" s="24"/>
     </row>
     <row r="386">
-      <c r="B386" s="29"/>
+      <c r="B386" s="24"/>
     </row>
     <row r="387">
-      <c r="B387" s="29"/>
+      <c r="B387" s="24"/>
     </row>
     <row r="388">
-      <c r="B388" s="29"/>
+      <c r="B388" s="24"/>
     </row>
     <row r="389">
-      <c r="B389" s="29"/>
+      <c r="B389" s="24"/>
     </row>
     <row r="390">
-      <c r="B390" s="29"/>
+      <c r="B390" s="24"/>
     </row>
     <row r="391">
-      <c r="B391" s="29"/>
+      <c r="B391" s="24"/>
     </row>
     <row r="392">
-      <c r="B392" s="29"/>
+      <c r="B392" s="24"/>
     </row>
     <row r="393">
-      <c r="B393" s="29"/>
+      <c r="B393" s="24"/>
     </row>
     <row r="394">
-      <c r="B394" s="29"/>
+      <c r="B394" s="24"/>
     </row>
     <row r="395">
-      <c r="B395" s="29"/>
+      <c r="B395" s="24"/>
     </row>
     <row r="396">
-      <c r="B396" s="29"/>
+      <c r="B396" s="24"/>
     </row>
     <row r="397">
-      <c r="B397" s="29"/>
+      <c r="B397" s="24"/>
     </row>
     <row r="398">
-      <c r="B398" s="29"/>
+      <c r="B398" s="24"/>
     </row>
     <row r="399">
-      <c r="B399" s="29"/>
+      <c r="B399" s="24"/>
     </row>
     <row r="400">
-      <c r="B400" s="29"/>
+      <c r="B400" s="24"/>
     </row>
     <row r="401">
-      <c r="B401" s="29"/>
+      <c r="B401" s="24"/>
     </row>
     <row r="402">
-      <c r="B402" s="29"/>
+      <c r="B402" s="24"/>
     </row>
     <row r="403">
-      <c r="B403" s="29"/>
+      <c r="B403" s="24"/>
     </row>
     <row r="404">
-      <c r="B404" s="29"/>
+      <c r="B404" s="24"/>
     </row>
     <row r="405">
-      <c r="B405" s="29"/>
+      <c r="B405" s="24"/>
     </row>
     <row r="406">
-      <c r="B406" s="29"/>
+      <c r="B406" s="24"/>
     </row>
     <row r="407">
-      <c r="B407" s="29"/>
+      <c r="B407" s="24"/>
     </row>
     <row r="408">
-      <c r="B408" s="29"/>
+      <c r="B408" s="24"/>
     </row>
     <row r="409">
-      <c r="B409" s="29"/>
+      <c r="B409" s="24"/>
     </row>
     <row r="410">
-      <c r="B410" s="29"/>
+      <c r="B410" s="24"/>
     </row>
     <row r="411">
-      <c r="B411" s="29"/>
+      <c r="B411" s="24"/>
     </row>
     <row r="412">
-      <c r="B412" s="29"/>
+      <c r="B412" s="24"/>
     </row>
     <row r="413">
-      <c r="B413" s="29"/>
+      <c r="B413" s="24"/>
     </row>
     <row r="414">
-      <c r="B414" s="29"/>
+      <c r="B414" s="24"/>
     </row>
     <row r="415">
-      <c r="B415" s="29"/>
+      <c r="B415" s="24"/>
     </row>
     <row r="416">
-      <c r="B416" s="29"/>
+      <c r="B416" s="24"/>
     </row>
     <row r="417">
-      <c r="B417" s="29"/>
+      <c r="B417" s="24"/>
     </row>
     <row r="418">
-      <c r="B418" s="29"/>
+      <c r="B418" s="24"/>
     </row>
     <row r="419">
-      <c r="B419" s="29"/>
+      <c r="B419" s="24"/>
     </row>
     <row r="420">
-      <c r="B420" s="29"/>
+      <c r="B420" s="24"/>
     </row>
     <row r="421">
-      <c r="B421" s="29"/>
+      <c r="B421" s="24"/>
     </row>
     <row r="422">
-      <c r="B422" s="29"/>
+      <c r="B422" s="24"/>
     </row>
     <row r="423">
-      <c r="B423" s="29"/>
+      <c r="B423" s="24"/>
     </row>
     <row r="424">
-      <c r="B424" s="29"/>
+      <c r="B424" s="24"/>
     </row>
     <row r="425">
-      <c r="B425" s="29"/>
+      <c r="B425" s="24"/>
     </row>
     <row r="426">
-      <c r="B426" s="29"/>
+      <c r="B426" s="24"/>
     </row>
     <row r="427">
-      <c r="B427" s="29"/>
+      <c r="B427" s="24"/>
     </row>
     <row r="428">
-      <c r="B428" s="29"/>
+      <c r="B428" s="24"/>
     </row>
     <row r="429">
-      <c r="B429" s="29"/>
+      <c r="B429" s="24"/>
     </row>
     <row r="430">
-      <c r="B430" s="29"/>
+      <c r="B430" s="24"/>
     </row>
     <row r="431">
-      <c r="B431" s="29"/>
+      <c r="B431" s="24"/>
     </row>
     <row r="432">
-      <c r="B432" s="29"/>
+      <c r="B432" s="24"/>
     </row>
     <row r="433">
-      <c r="B433" s="29"/>
+      <c r="B433" s="24"/>
     </row>
     <row r="434">
-      <c r="B434" s="29"/>
+      <c r="B434" s="24"/>
     </row>
     <row r="435">
-      <c r="B435" s="29"/>
+      <c r="B435" s="24"/>
     </row>
     <row r="436">
-      <c r="B436" s="29"/>
+      <c r="B436" s="24"/>
     </row>
     <row r="437">
-      <c r="B437" s="29"/>
+      <c r="B437" s="24"/>
     </row>
     <row r="438">
-      <c r="B438" s="29"/>
+      <c r="B438" s="24"/>
     </row>
     <row r="439">
-      <c r="B439" s="29"/>
+      <c r="B439" s="24"/>
     </row>
     <row r="440">
-      <c r="B440" s="29"/>
+      <c r="B440" s="24"/>
     </row>
     <row r="441">
-      <c r="B441" s="29"/>
+      <c r="B441" s="24"/>
     </row>
     <row r="442">
-      <c r="B442" s="29"/>
+      <c r="B442" s="24"/>
     </row>
     <row r="443">
-      <c r="B443" s="29"/>
+      <c r="B443" s="24"/>
     </row>
     <row r="444">
-      <c r="B444" s="29"/>
+      <c r="B444" s="24"/>
     </row>
     <row r="445">
-      <c r="B445" s="29"/>
+      <c r="B445" s="24"/>
     </row>
     <row r="446">
-      <c r="B446" s="29"/>
+      <c r="B446" s="24"/>
     </row>
     <row r="447">
-      <c r="B447" s="29"/>
+      <c r="B447" s="24"/>
     </row>
     <row r="448">
-      <c r="B448" s="29"/>
+      <c r="B448" s="24"/>
     </row>
     <row r="449">
-      <c r="B449" s="29"/>
+      <c r="B449" s="24"/>
     </row>
     <row r="450">
-      <c r="B450" s="29"/>
+      <c r="B450" s="24"/>
     </row>
     <row r="451">
-      <c r="B451" s="29"/>
+      <c r="B451" s="24"/>
     </row>
     <row r="452">
-      <c r="B452" s="29"/>
+      <c r="B452" s="24"/>
     </row>
     <row r="453">
-      <c r="B453" s="29"/>
+      <c r="B453" s="24"/>
     </row>
     <row r="454">
-      <c r="B454" s="29"/>
+      <c r="B454" s="24"/>
     </row>
     <row r="455">
-      <c r="B455" s="29"/>
+      <c r="B455" s="24"/>
     </row>
     <row r="456">
-      <c r="B456" s="29"/>
+      <c r="B456" s="24"/>
     </row>
     <row r="457">
-      <c r="B457" s="29"/>
+      <c r="B457" s="24"/>
     </row>
     <row r="458">
-      <c r="B458" s="29"/>
+      <c r="B458" s="24"/>
     </row>
     <row r="459">
-      <c r="B459" s="29"/>
+      <c r="B459" s="24"/>
     </row>
     <row r="460">
-      <c r="B460" s="29"/>
+      <c r="B460" s="24"/>
     </row>
     <row r="461">
-      <c r="B461" s="29"/>
+      <c r="B461" s="24"/>
     </row>
     <row r="462">
-      <c r="B462" s="29"/>
+      <c r="B462" s="24"/>
     </row>
     <row r="463">
-      <c r="B463" s="29"/>
+      <c r="B463" s="24"/>
     </row>
     <row r="464">
-      <c r="B464" s="29"/>
+      <c r="B464" s="24"/>
     </row>
     <row r="465">
-      <c r="B465" s="29"/>
+      <c r="B465" s="24"/>
     </row>
     <row r="466">
-      <c r="B466" s="29"/>
+      <c r="B466" s="24"/>
     </row>
     <row r="467">
-      <c r="B467" s="29"/>
+      <c r="B467" s="24"/>
     </row>
     <row r="468">
-      <c r="B468" s="29"/>
+      <c r="B468" s="24"/>
     </row>
     <row r="469">
-      <c r="B469" s="29"/>
+      <c r="B469" s="24"/>
     </row>
     <row r="470">
-      <c r="B470" s="29"/>
+      <c r="B470" s="24"/>
     </row>
     <row r="471">
-      <c r="B471" s="29"/>
+      <c r="B471" s="24"/>
     </row>
     <row r="472">
-      <c r="B472" s="29"/>
+      <c r="B472" s="24"/>
     </row>
     <row r="473">
-      <c r="B473" s="29"/>
+      <c r="B473" s="24"/>
     </row>
     <row r="474">
-      <c r="B474" s="29"/>
+      <c r="B474" s="24"/>
     </row>
     <row r="475">
-      <c r="B475" s="29"/>
+      <c r="B475" s="24"/>
     </row>
     <row r="476">
-      <c r="B476" s="29"/>
+      <c r="B476" s="24"/>
     </row>
     <row r="477">
-      <c r="B477" s="29"/>
+      <c r="B477" s="24"/>
     </row>
     <row r="478">
-      <c r="B478" s="29"/>
+      <c r="B478" s="24"/>
     </row>
     <row r="479">
-      <c r="B479" s="29"/>
+      <c r="B479" s="24"/>
     </row>
     <row r="480">
-      <c r="B480" s="29"/>
+      <c r="B480" s="24"/>
     </row>
     <row r="481">
-      <c r="B481" s="29"/>
+      <c r="B481" s="24"/>
     </row>
     <row r="482">
-      <c r="B482" s="29"/>
+      <c r="B482" s="24"/>
     </row>
     <row r="483">
-      <c r="B483" s="29"/>
+      <c r="B483" s="24"/>
     </row>
     <row r="484">
-      <c r="B484" s="29"/>
+      <c r="B484" s="24"/>
     </row>
     <row r="485">
-      <c r="B485" s="29"/>
+      <c r="B485" s="24"/>
     </row>
     <row r="486">
-      <c r="B486" s="29"/>
+      <c r="B486" s="24"/>
     </row>
     <row r="487">
-      <c r="B487" s="29"/>
+      <c r="B487" s="24"/>
     </row>
     <row r="488">
-      <c r="B488" s="29"/>
+      <c r="B488" s="24"/>
     </row>
     <row r="489">
-      <c r="B489" s="29"/>
+      <c r="B489" s="24"/>
     </row>
     <row r="490">
-      <c r="B490" s="29"/>
+      <c r="B490" s="24"/>
     </row>
     <row r="491">
-      <c r="B491" s="29"/>
+      <c r="B491" s="24"/>
     </row>
     <row r="492">
-      <c r="B492" s="29"/>
+      <c r="B492" s="24"/>
     </row>
     <row r="493">
-      <c r="B493" s="29"/>
+      <c r="B493" s="24"/>
     </row>
     <row r="494">
-      <c r="B494" s="29"/>
+      <c r="B494" s="24"/>
     </row>
     <row r="495">
-      <c r="B495" s="29"/>
+      <c r="B495" s="24"/>
     </row>
     <row r="496">
-      <c r="B496" s="29"/>
+      <c r="B496" s="24"/>
     </row>
     <row r="497">
-      <c r="B497" s="29"/>
+      <c r="B497" s="24"/>
     </row>
     <row r="498">
-      <c r="B498" s="29"/>
+      <c r="B498" s="24"/>
     </row>
     <row r="499">
-      <c r="B499" s="29"/>
+      <c r="B499" s="24"/>
     </row>
     <row r="500">
-      <c r="B500" s="29"/>
+      <c r="B500" s="24"/>
     </row>
     <row r="501">
-      <c r="B501" s="29"/>
+      <c r="B501" s="24"/>
     </row>
     <row r="502">
-      <c r="B502" s="29"/>
+      <c r="B502" s="24"/>
     </row>
     <row r="503">
-      <c r="B503" s="29"/>
+      <c r="B503" s="24"/>
     </row>
     <row r="504">
-      <c r="B504" s="29"/>
+      <c r="B504" s="24"/>
     </row>
     <row r="505">
-      <c r="B505" s="29"/>
+      <c r="B505" s="24"/>
     </row>
     <row r="506">
-      <c r="B506" s="29"/>
+      <c r="B506" s="24"/>
     </row>
     <row r="507">
-      <c r="B507" s="29"/>
+      <c r="B507" s="24"/>
     </row>
     <row r="508">
-      <c r="B508" s="29"/>
+      <c r="B508" s="24"/>
     </row>
     <row r="509">
-      <c r="B509" s="29"/>
+      <c r="B509" s="24"/>
     </row>
     <row r="510">
-      <c r="B510" s="29"/>
+      <c r="B510" s="24"/>
     </row>
     <row r="511">
-      <c r="B511" s="29"/>
+      <c r="B511" s="24"/>
     </row>
     <row r="512">
-      <c r="B512" s="29"/>
+      <c r="B512" s="24"/>
     </row>
     <row r="513">
-      <c r="B513" s="29"/>
+      <c r="B513" s="24"/>
     </row>
     <row r="514">
-      <c r="B514" s="29"/>
+      <c r="B514" s="24"/>
     </row>
     <row r="515">
-      <c r="B515" s="29"/>
+      <c r="B515" s="24"/>
     </row>
     <row r="516">
-      <c r="B516" s="29"/>
+      <c r="B516" s="24"/>
     </row>
     <row r="517">
-      <c r="B517" s="29"/>
+      <c r="B517" s="24"/>
     </row>
     <row r="518">
-      <c r="B518" s="29"/>
+      <c r="B518" s="24"/>
     </row>
     <row r="519">
-      <c r="B519" s="29"/>
+      <c r="B519" s="24"/>
     </row>
     <row r="520">
-      <c r="B520" s="29"/>
+      <c r="B520" s="24"/>
     </row>
     <row r="521">
-      <c r="B521" s="29"/>
+      <c r="B521" s="24"/>
     </row>
     <row r="522">
-      <c r="B522" s="29"/>
+      <c r="B522" s="24"/>
     </row>
     <row r="523">
-      <c r="B523" s="29"/>
+      <c r="B523" s="24"/>
     </row>
     <row r="524">
-      <c r="B524" s="29"/>
+      <c r="B524" s="24"/>
     </row>
     <row r="525">
-      <c r="B525" s="29"/>
+      <c r="B525" s="24"/>
     </row>
     <row r="526">
-      <c r="B526" s="29"/>
+      <c r="B526" s="24"/>
     </row>
     <row r="527">
-      <c r="B527" s="29"/>
+      <c r="B527" s="24"/>
     </row>
     <row r="528">
-      <c r="B528" s="29"/>
+      <c r="B528" s="24"/>
     </row>
     <row r="529">
-      <c r="B529" s="29"/>
+      <c r="B529" s="24"/>
     </row>
     <row r="530">
-      <c r="B530" s="29"/>
+      <c r="B530" s="24"/>
     </row>
     <row r="531">
-      <c r="B531" s="29"/>
+      <c r="B531" s="24"/>
     </row>
     <row r="532">
-      <c r="B532" s="29"/>
+      <c r="B532" s="24"/>
     </row>
     <row r="533">
-      <c r="B533" s="29"/>
+      <c r="B533" s="24"/>
     </row>
     <row r="534">
-      <c r="B534" s="29"/>
+      <c r="B534" s="24"/>
     </row>
     <row r="535">
-      <c r="B535" s="29"/>
+      <c r="B535" s="24"/>
     </row>
     <row r="536">
-      <c r="B536" s="29"/>
+      <c r="B536" s="24"/>
     </row>
     <row r="537">
-      <c r="B537" s="29"/>
+      <c r="B537" s="24"/>
     </row>
     <row r="538">
-      <c r="B538" s="29"/>
+      <c r="B538" s="24"/>
     </row>
     <row r="539">
-      <c r="B539" s="29"/>
+      <c r="B539" s="24"/>
     </row>
     <row r="540">
-      <c r="B540" s="29"/>
+      <c r="B540" s="24"/>
     </row>
     <row r="541">
-      <c r="B541" s="29"/>
+      <c r="B541" s="24"/>
     </row>
     <row r="542">
-      <c r="B542" s="29"/>
+      <c r="B542" s="24"/>
     </row>
     <row r="543">
-      <c r="B543" s="29"/>
+      <c r="B543" s="24"/>
     </row>
     <row r="544">
-      <c r="B544" s="29"/>
+      <c r="B544" s="24"/>
     </row>
     <row r="545">
-      <c r="B545" s="29"/>
+      <c r="B545" s="24"/>
     </row>
     <row r="546">
-      <c r="B546" s="29"/>
+      <c r="B546" s="24"/>
     </row>
     <row r="547">
-      <c r="B547" s="29"/>
+      <c r="B547" s="24"/>
     </row>
     <row r="548">
-      <c r="B548" s="29"/>
+      <c r="B548" s="24"/>
     </row>
     <row r="549">
-      <c r="B549" s="29"/>
+      <c r="B549" s="24"/>
     </row>
     <row r="550">
-      <c r="B550" s="29"/>
+      <c r="B550" s="24"/>
     </row>
     <row r="551">
-      <c r="B551" s="29"/>
+      <c r="B551" s="24"/>
     </row>
     <row r="552">
-      <c r="B552" s="29"/>
+      <c r="B552" s="24"/>
     </row>
     <row r="553">
-      <c r="B553" s="29"/>
+      <c r="B553" s="24"/>
     </row>
     <row r="554">
-      <c r="B554" s="29"/>
+      <c r="B554" s="24"/>
     </row>
     <row r="555">
-      <c r="B555" s="29"/>
+      <c r="B555" s="24"/>
     </row>
     <row r="556">
-      <c r="B556" s="29"/>
+      <c r="B556" s="24"/>
     </row>
     <row r="557">
-      <c r="B557" s="29"/>
+      <c r="B557" s="24"/>
     </row>
     <row r="558">
-      <c r="B558" s="29"/>
+      <c r="B558" s="24"/>
     </row>
     <row r="559">
-      <c r="B559" s="29"/>
+      <c r="B559" s="24"/>
     </row>
     <row r="560">
-      <c r="B560" s="29"/>
+      <c r="B560" s="24"/>
     </row>
     <row r="561">
-      <c r="B561" s="29"/>
+      <c r="B561" s="24"/>
     </row>
     <row r="562">
-      <c r="B562" s="29"/>
+      <c r="B562" s="24"/>
     </row>
     <row r="563">
-      <c r="B563" s="29"/>
+      <c r="B563" s="24"/>
     </row>
     <row r="564">
-      <c r="B564" s="29"/>
+      <c r="B564" s="24"/>
     </row>
     <row r="565">
-      <c r="B565" s="29"/>
+      <c r="B565" s="24"/>
     </row>
     <row r="566">
-      <c r="B566" s="29"/>
+      <c r="B566" s="24"/>
     </row>
     <row r="567">
-      <c r="B567" s="29"/>
+      <c r="B567" s="24"/>
     </row>
     <row r="568">
-      <c r="B568" s="29"/>
+      <c r="B568" s="24"/>
     </row>
     <row r="569">
-      <c r="B569" s="29"/>
+      <c r="B569" s="24"/>
     </row>
     <row r="570">
-      <c r="B570" s="29"/>
+      <c r="B570" s="24"/>
     </row>
     <row r="571">
-      <c r="B571" s="29"/>
+      <c r="B571" s="24"/>
     </row>
     <row r="572">
-      <c r="B572" s="29"/>
+      <c r="B572" s="24"/>
     </row>
     <row r="573">
-      <c r="B573" s="29"/>
+      <c r="B573" s="24"/>
     </row>
     <row r="574">
-      <c r="B574" s="29"/>
+      <c r="B574" s="24"/>
     </row>
     <row r="575">
-      <c r="B575" s="29"/>
+      <c r="B575" s="24"/>
     </row>
     <row r="576">
-      <c r="B576" s="29"/>
+      <c r="B576" s="24"/>
     </row>
     <row r="577">
-      <c r="B577" s="29"/>
+      <c r="B577" s="24"/>
     </row>
     <row r="578">
-      <c r="B578" s="29"/>
+      <c r="B578" s="24"/>
     </row>
     <row r="579">
-      <c r="B579" s="29"/>
+      <c r="B579" s="24"/>
     </row>
     <row r="580">
-      <c r="B580" s="29"/>
+      <c r="B580" s="24"/>
     </row>
     <row r="581">
-      <c r="B581" s="29"/>
+      <c r="B581" s="24"/>
     </row>
     <row r="582">
-      <c r="B582" s="29"/>
+      <c r="B582" s="24"/>
     </row>
     <row r="583">
-      <c r="B583" s="29"/>
+      <c r="B583" s="24"/>
     </row>
     <row r="584">
-      <c r="B584" s="29"/>
+      <c r="B584" s="24"/>
     </row>
     <row r="585">
-      <c r="B585" s="29"/>
+      <c r="B585" s="24"/>
     </row>
     <row r="586">
-      <c r="B586" s="29"/>
+      <c r="B586" s="24"/>
     </row>
     <row r="587">
-      <c r="B587" s="29"/>
+      <c r="B587" s="24"/>
     </row>
     <row r="588">
-      <c r="B588" s="29"/>
+      <c r="B588" s="24"/>
     </row>
     <row r="589">
-      <c r="B589" s="29"/>
+      <c r="B589" s="24"/>
     </row>
     <row r="590">
-      <c r="B590" s="29"/>
+      <c r="B590" s="24"/>
     </row>
     <row r="591">
-      <c r="B591" s="29"/>
+      <c r="B591" s="24"/>
     </row>
     <row r="592">
-      <c r="B592" s="29"/>
+      <c r="B592" s="24"/>
     </row>
     <row r="593">
-      <c r="B593" s="29"/>
+      <c r="B593" s="24"/>
     </row>
     <row r="594">
-      <c r="B594" s="29"/>
+      <c r="B594" s="24"/>
     </row>
     <row r="595">
-      <c r="B595" s="29"/>
+      <c r="B595" s="24"/>
     </row>
     <row r="596">
-      <c r="B596" s="29"/>
+      <c r="B596" s="24"/>
     </row>
     <row r="597">
-      <c r="B597" s="29"/>
+      <c r="B597" s="24"/>
     </row>
     <row r="598">
-      <c r="B598" s="29"/>
+      <c r="B598" s="24"/>
     </row>
     <row r="599">
-      <c r="B599" s="29"/>
+      <c r="B599" s="24"/>
     </row>
     <row r="600">
-      <c r="B600" s="29"/>
+      <c r="B600" s="24"/>
     </row>
     <row r="601">
-      <c r="B601" s="29"/>
+      <c r="B601" s="24"/>
     </row>
     <row r="602">
-      <c r="B602" s="29"/>
+      <c r="B602" s="24"/>
     </row>
     <row r="603">
-      <c r="B603" s="29"/>
+      <c r="B603" s="24"/>
     </row>
     <row r="604">
-      <c r="B604" s="29"/>
+      <c r="B604" s="24"/>
     </row>
     <row r="605">
-      <c r="B605" s="29"/>
+      <c r="B605" s="24"/>
     </row>
     <row r="606">
-      <c r="B606" s="29"/>
+      <c r="B606" s="24"/>
     </row>
     <row r="607">
-      <c r="B607" s="29"/>
+      <c r="B607" s="24"/>
     </row>
     <row r="608">
-      <c r="B608" s="29"/>
+      <c r="B608" s="24"/>
     </row>
     <row r="609">
-      <c r="B609" s="29"/>
+      <c r="B609" s="24"/>
     </row>
     <row r="610">
-      <c r="B610" s="29"/>
+      <c r="B610" s="24"/>
     </row>
     <row r="611">
-      <c r="B611" s="29"/>
+      <c r="B611" s="24"/>
     </row>
     <row r="612">
-      <c r="B612" s="29"/>
+      <c r="B612" s="24"/>
     </row>
     <row r="613">
-      <c r="B613" s="29"/>
+      <c r="B613" s="24"/>
     </row>
     <row r="614">
-      <c r="B614" s="29"/>
+      <c r="B614" s="24"/>
     </row>
     <row r="615">
-      <c r="B615" s="29"/>
+      <c r="B615" s="24"/>
     </row>
     <row r="616">
-      <c r="B616" s="29"/>
+      <c r="B616" s="24"/>
     </row>
     <row r="617">
-      <c r="B617" s="29"/>
+      <c r="B617" s="24"/>
     </row>
     <row r="618">
-      <c r="B618" s="29"/>
+      <c r="B618" s="24"/>
     </row>
     <row r="619">
-      <c r="B619" s="29"/>
+      <c r="B619" s="24"/>
     </row>
     <row r="620">
-      <c r="B620" s="29"/>
+      <c r="B620" s="24"/>
     </row>
     <row r="621">
-      <c r="B621" s="29"/>
+      <c r="B621" s="24"/>
     </row>
     <row r="622">
-      <c r="B622" s="29"/>
+      <c r="B622" s="24"/>
     </row>
     <row r="623">
-      <c r="B623" s="29"/>
+      <c r="B623" s="24"/>
     </row>
     <row r="624">
-      <c r="B624" s="29"/>
+      <c r="B624" s="24"/>
     </row>
     <row r="625">
-      <c r="B625" s="29"/>
+      <c r="B625" s="24"/>
     </row>
     <row r="626">
-      <c r="B626" s="29"/>
+      <c r="B626" s="24"/>
     </row>
     <row r="627">
-      <c r="B627" s="29"/>
+      <c r="B627" s="24"/>
     </row>
     <row r="628">
-      <c r="B628" s="29"/>
+      <c r="B628" s="24"/>
     </row>
     <row r="629">
-      <c r="B629" s="29"/>
+      <c r="B629" s="24"/>
     </row>
     <row r="630">
-      <c r="B630" s="29"/>
+      <c r="B630" s="24"/>
     </row>
     <row r="631">
-      <c r="B631" s="29"/>
+      <c r="B631" s="24"/>
     </row>
     <row r="632">
-      <c r="B632" s="29"/>
+      <c r="B632" s="24"/>
     </row>
     <row r="633">
-      <c r="B633" s="29"/>
+      <c r="B633" s="24"/>
     </row>
     <row r="634">
-      <c r="B634" s="29"/>
+      <c r="B634" s="24"/>
     </row>
     <row r="635">
-      <c r="B635" s="29"/>
+      <c r="B635" s="24"/>
     </row>
     <row r="636">
-      <c r="B636" s="29"/>
+      <c r="B636" s="24"/>
     </row>
     <row r="637">
-      <c r="B637" s="29"/>
+      <c r="B637" s="24"/>
     </row>
     <row r="638">
-      <c r="B638" s="29"/>
+      <c r="B638" s="24"/>
     </row>
     <row r="639">
-      <c r="B639" s="29"/>
+      <c r="B639" s="24"/>
     </row>
     <row r="640">
-      <c r="B640" s="29"/>
+      <c r="B640" s="24"/>
     </row>
     <row r="641">
-      <c r="B641" s="29"/>
+      <c r="B641" s="24"/>
     </row>
     <row r="642">
-      <c r="B642" s="29"/>
+      <c r="B642" s="24"/>
     </row>
     <row r="643">
-      <c r="B643" s="29"/>
+      <c r="B643" s="24"/>
     </row>
     <row r="644">
-      <c r="B644" s="29"/>
+      <c r="B644" s="24"/>
     </row>
     <row r="645">
-      <c r="B645" s="29"/>
+      <c r="B645" s="24"/>
     </row>
     <row r="646">
-      <c r="B646" s="29"/>
+      <c r="B646" s="24"/>
     </row>
     <row r="647">
-      <c r="B647" s="29"/>
+      <c r="B647" s="24"/>
     </row>
     <row r="648">
-      <c r="B648" s="29"/>
+      <c r="B648" s="24"/>
     </row>
     <row r="649">
-      <c r="B649" s="29"/>
+      <c r="B649" s="24"/>
     </row>
     <row r="650">
-      <c r="B650" s="29"/>
+      <c r="B650" s="24"/>
     </row>
     <row r="651">
-      <c r="B651" s="29"/>
+      <c r="B651" s="24"/>
     </row>
     <row r="652">
-      <c r="B652" s="29"/>
+      <c r="B652" s="24"/>
     </row>
     <row r="653">
-      <c r="B653" s="29"/>
+      <c r="B653" s="24"/>
     </row>
     <row r="654">
-      <c r="B654" s="29"/>
+      <c r="B654" s="24"/>
     </row>
     <row r="655">
-      <c r="B655" s="29"/>
+      <c r="B655" s="24"/>
     </row>
     <row r="656">
-      <c r="B656" s="29"/>
+      <c r="B656" s="24"/>
     </row>
     <row r="657">
-      <c r="B657" s="29"/>
+      <c r="B657" s="24"/>
     </row>
     <row r="658">
-      <c r="B658" s="29"/>
+      <c r="B658" s="24"/>
     </row>
     <row r="659">
-      <c r="B659" s="29"/>
+      <c r="B659" s="24"/>
     </row>
     <row r="660">
-      <c r="B660" s="29"/>
+      <c r="B660" s="24"/>
     </row>
     <row r="661">
-      <c r="B661" s="29"/>
+      <c r="B661" s="24"/>
     </row>
     <row r="662">
-      <c r="B662" s="29"/>
+      <c r="B662" s="24"/>
     </row>
     <row r="663">
-      <c r="B663" s="29"/>
+      <c r="B663" s="24"/>
     </row>
     <row r="664">
-      <c r="B664" s="29"/>
+      <c r="B664" s="24"/>
     </row>
     <row r="665">
-      <c r="B665" s="29"/>
+      <c r="B665" s="24"/>
     </row>
     <row r="666">
-      <c r="B666" s="29"/>
+      <c r="B666" s="24"/>
     </row>
     <row r="667">
-      <c r="B667" s="29"/>
+      <c r="B667" s="24"/>
     </row>
     <row r="668">
-      <c r="B668" s="29"/>
+      <c r="B668" s="24"/>
     </row>
     <row r="669">
-      <c r="B669" s="29"/>
+      <c r="B669" s="24"/>
     </row>
     <row r="670">
-      <c r="B670" s="29"/>
+      <c r="B670" s="24"/>
     </row>
     <row r="671">
-      <c r="B671" s="29"/>
+      <c r="B671" s="24"/>
     </row>
     <row r="672">
-      <c r="B672" s="29"/>
+      <c r="B672" s="24"/>
     </row>
     <row r="673">
-      <c r="B673" s="29"/>
+      <c r="B673" s="24"/>
     </row>
     <row r="674">
-      <c r="B674" s="29"/>
+      <c r="B674" s="24"/>
     </row>
     <row r="675">
-      <c r="B675" s="29"/>
+      <c r="B675" s="24"/>
     </row>
     <row r="676">
-      <c r="B676" s="29"/>
+      <c r="B676" s="24"/>
     </row>
     <row r="677">
-      <c r="B677" s="29"/>
+      <c r="B677" s="24"/>
     </row>
     <row r="678">
-      <c r="B678" s="29"/>
+      <c r="B678" s="24"/>
     </row>
     <row r="679">
-      <c r="B679" s="29"/>
+      <c r="B679" s="24"/>
     </row>
     <row r="680">
-      <c r="B680" s="29"/>
+      <c r="B680" s="24"/>
     </row>
     <row r="681">
-      <c r="B681" s="29"/>
+      <c r="B681" s="24"/>
     </row>
     <row r="682">
-      <c r="B682" s="29"/>
+      <c r="B682" s="24"/>
     </row>
     <row r="683">
-      <c r="B683" s="29"/>
+      <c r="B683" s="24"/>
     </row>
     <row r="684">
-      <c r="B684" s="29"/>
+      <c r="B684" s="24"/>
     </row>
     <row r="685">
-      <c r="B685" s="29"/>
+      <c r="B685" s="24"/>
     </row>
     <row r="686">
-      <c r="B686" s="29"/>
+      <c r="B686" s="24"/>
     </row>
     <row r="687">
-      <c r="B687" s="29"/>
+      <c r="B687" s="24"/>
     </row>
     <row r="688">
-      <c r="B688" s="29"/>
+      <c r="B688" s="24"/>
     </row>
     <row r="689">
-      <c r="B689" s="29"/>
+      <c r="B689" s="24"/>
     </row>
     <row r="690">
-      <c r="B690" s="29"/>
+      <c r="B690" s="24"/>
     </row>
     <row r="691">
-      <c r="B691" s="29"/>
+      <c r="B691" s="24"/>
     </row>
     <row r="692">
-      <c r="B692" s="29"/>
+      <c r="B692" s="24"/>
     </row>
     <row r="693">
-      <c r="B693" s="29"/>
+      <c r="B693" s="24"/>
     </row>
     <row r="694">
-      <c r="B694" s="29"/>
+      <c r="B694" s="24"/>
     </row>
     <row r="695">
-      <c r="B695" s="29"/>
+      <c r="B695" s="24"/>
     </row>
     <row r="696">
-      <c r="B696" s="29"/>
+      <c r="B696" s="24"/>
     </row>
     <row r="697">
-      <c r="B697" s="29"/>
+      <c r="B697" s="24"/>
     </row>
     <row r="698">
-      <c r="B698" s="29"/>
+      <c r="B698" s="24"/>
     </row>
     <row r="699">
-      <c r="B699" s="29"/>
+      <c r="B699" s="24"/>
     </row>
     <row r="700">
-      <c r="B700" s="29"/>
+      <c r="B700" s="24"/>
     </row>
     <row r="701">
-      <c r="B701" s="29"/>
+      <c r="B701" s="24"/>
     </row>
     <row r="702">
-      <c r="B702" s="29"/>
+      <c r="B702" s="24"/>
     </row>
     <row r="703">
-      <c r="B703" s="29"/>
+      <c r="B703" s="24"/>
     </row>
     <row r="704">
-      <c r="B704" s="29"/>
+      <c r="B704" s="24"/>
     </row>
     <row r="705">
-      <c r="B705" s="29"/>
+      <c r="B705" s="24"/>
     </row>
     <row r="706">
-      <c r="B706" s="29"/>
+      <c r="B706" s="24"/>
     </row>
     <row r="707">
-      <c r="B707" s="29"/>
+      <c r="B707" s="24"/>
     </row>
     <row r="708">
-      <c r="B708" s="29"/>
+      <c r="B708" s="24"/>
     </row>
     <row r="709">
-      <c r="B709" s="29"/>
+      <c r="B709" s="24"/>
     </row>
     <row r="710">
-      <c r="B710" s="29"/>
+      <c r="B710" s="24"/>
     </row>
     <row r="711">
-      <c r="B711" s="29"/>
+      <c r="B711" s="24"/>
     </row>
     <row r="712">
-      <c r="B712" s="29"/>
+      <c r="B712" s="24"/>
     </row>
     <row r="713">
-      <c r="B713" s="29"/>
+      <c r="B713" s="24"/>
     </row>
     <row r="714">
-      <c r="B714" s="29"/>
+      <c r="B714" s="24"/>
     </row>
     <row r="715">
-      <c r="B715" s="29"/>
+      <c r="B715" s="24"/>
     </row>
     <row r="716">
-      <c r="B716" s="29"/>
+      <c r="B716" s="24"/>
     </row>
     <row r="717">
-      <c r="B717" s="29"/>
+      <c r="B717" s="24"/>
     </row>
     <row r="718">
-      <c r="B718" s="29"/>
+      <c r="B718" s="24"/>
     </row>
     <row r="719">
-      <c r="B719" s="29"/>
+      <c r="B719" s="24"/>
     </row>
     <row r="720">
-      <c r="B720" s="29"/>
+      <c r="B720" s="24"/>
     </row>
     <row r="721">
-      <c r="B721" s="29"/>
+      <c r="B721" s="24"/>
     </row>
     <row r="722">
-      <c r="B722" s="29"/>
+      <c r="B722" s="24"/>
     </row>
     <row r="723">
-      <c r="B723" s="29"/>
+      <c r="B723" s="24"/>
     </row>
     <row r="724">
-      <c r="B724" s="29"/>
+      <c r="B724" s="24"/>
     </row>
     <row r="725">
-      <c r="B725" s="29"/>
+      <c r="B725" s="24"/>
     </row>
     <row r="726">
-      <c r="B726" s="29"/>
+      <c r="B726" s="24"/>
     </row>
     <row r="727">
-      <c r="B727" s="29"/>
+      <c r="B727" s="24"/>
     </row>
     <row r="728">
-      <c r="B728" s="29"/>
+      <c r="B728" s="24"/>
     </row>
     <row r="729">
-      <c r="B729" s="29"/>
+      <c r="B729" s="24"/>
     </row>
     <row r="730">
-      <c r="B730" s="29"/>
+      <c r="B730" s="24"/>
     </row>
     <row r="731">
-      <c r="B731" s="29"/>
+      <c r="B731" s="24"/>
     </row>
     <row r="732">
-      <c r="B732" s="29"/>
+      <c r="B732" s="24"/>
     </row>
     <row r="733">
-      <c r="B733" s="29"/>
+      <c r="B733" s="24"/>
     </row>
     <row r="734">
-      <c r="B734" s="29"/>
+      <c r="B734" s="24"/>
     </row>
     <row r="735">
-      <c r="B735" s="29"/>
+      <c r="B735" s="24"/>
     </row>
     <row r="736">
-      <c r="B736" s="29"/>
+      <c r="B736" s="24"/>
     </row>
     <row r="737">
-      <c r="B737" s="29"/>
+      <c r="B737" s="24"/>
     </row>
     <row r="738">
-      <c r="B738" s="29"/>
+      <c r="B738" s="24"/>
     </row>
     <row r="739">
-      <c r="B739" s="29"/>
+      <c r="B739" s="24"/>
     </row>
     <row r="740">
-      <c r="B740" s="29"/>
+      <c r="B740" s="24"/>
     </row>
     <row r="741">
-      <c r="B741" s="29"/>
+      <c r="B741" s="24"/>
     </row>
     <row r="742">
-      <c r="B742" s="29"/>
+      <c r="B742" s="24"/>
     </row>
     <row r="743">
-      <c r="B743" s="29"/>
+      <c r="B743" s="24"/>
     </row>
     <row r="744">
-      <c r="B744" s="29"/>
+      <c r="B744" s="24"/>
     </row>
     <row r="745">
-      <c r="B745" s="29"/>
+      <c r="B745" s="24"/>
     </row>
     <row r="746">
-      <c r="B746" s="29"/>
+      <c r="B746" s="24"/>
     </row>
     <row r="747">
-      <c r="B747" s="29"/>
+      <c r="B747" s="24"/>
     </row>
     <row r="748">
-      <c r="B748" s="29"/>
+      <c r="B748" s="24"/>
     </row>
     <row r="749">
-      <c r="B749" s="29"/>
+      <c r="B749" s="24"/>
     </row>
     <row r="750">
-      <c r="B750" s="29"/>
+      <c r="B750" s="24"/>
     </row>
     <row r="751">
-      <c r="B751" s="29"/>
+      <c r="B751" s="24"/>
     </row>
     <row r="752">
-      <c r="B752" s="29"/>
+      <c r="B752" s="24"/>
     </row>
     <row r="753">
-      <c r="B753" s="29"/>
+      <c r="B753" s="24"/>
     </row>
     <row r="754">
-      <c r="B754" s="29"/>
+      <c r="B754" s="24"/>
     </row>
     <row r="755">
-      <c r="B755" s="29"/>
+      <c r="B755" s="24"/>
     </row>
     <row r="756">
-      <c r="B756" s="29"/>
+      <c r="B756" s="24"/>
     </row>
     <row r="757">
-      <c r="B757" s="29"/>
+      <c r="B757" s="24"/>
     </row>
     <row r="758">
-      <c r="B758" s="29"/>
+      <c r="B758" s="24"/>
     </row>
     <row r="759">
-      <c r="B759" s="29"/>
+      <c r="B759" s="24"/>
     </row>
     <row r="760">
-      <c r="B760" s="29"/>
+      <c r="B760" s="24"/>
     </row>
     <row r="761">
-      <c r="B761" s="29"/>
+      <c r="B761" s="24"/>
     </row>
     <row r="762">
-      <c r="B762" s="29"/>
+      <c r="B762" s="24"/>
     </row>
     <row r="763">
-      <c r="B763" s="29"/>
+      <c r="B763" s="24"/>
     </row>
     <row r="764">
-      <c r="B764" s="29"/>
+      <c r="B764" s="24"/>
     </row>
     <row r="765">
-      <c r="B765" s="29"/>
+      <c r="B765" s="24"/>
     </row>
     <row r="766">
-      <c r="B766" s="29"/>
+      <c r="B766" s="24"/>
     </row>
     <row r="767">
-      <c r="B767" s="29"/>
+      <c r="B767" s="24"/>
     </row>
     <row r="768">
-      <c r="B768" s="29"/>
+      <c r="B768" s="24"/>
     </row>
     <row r="769">
-      <c r="B769" s="29"/>
+      <c r="B769" s="24"/>
     </row>
     <row r="770">
-      <c r="B770" s="29"/>
+      <c r="B770" s="24"/>
     </row>
     <row r="771">
-      <c r="B771" s="29"/>
+      <c r="B771" s="24"/>
     </row>
     <row r="772">
-      <c r="B772" s="29"/>
+      <c r="B772" s="24"/>
     </row>
     <row r="773">
-      <c r="B773" s="29"/>
+      <c r="B773" s="24"/>
     </row>
     <row r="774">
-      <c r="B774" s="29"/>
+      <c r="B774" s="24"/>
     </row>
     <row r="775">
-      <c r="B775" s="29"/>
+      <c r="B775" s="24"/>
     </row>
     <row r="776">
-      <c r="B776" s="29"/>
+      <c r="B776" s="24"/>
     </row>
     <row r="777">
-      <c r="B777" s="29"/>
+      <c r="B777" s="24"/>
     </row>
     <row r="778">
-      <c r="B778" s="29"/>
+      <c r="B778" s="24"/>
     </row>
     <row r="779">
-      <c r="B779" s="29"/>
+      <c r="B779" s="24"/>
     </row>
     <row r="780">
-      <c r="B780" s="29"/>
+      <c r="B780" s="24"/>
     </row>
     <row r="781">
-      <c r="B781" s="29"/>
+      <c r="B781" s="24"/>
     </row>
     <row r="782">
-      <c r="B782" s="29"/>
+      <c r="B782" s="24"/>
     </row>
     <row r="783">
-      <c r="B783" s="29"/>
+      <c r="B783" s="24"/>
     </row>
     <row r="784">
-      <c r="B784" s="29"/>
+      <c r="B784" s="24"/>
     </row>
     <row r="785">
-      <c r="B785" s="29"/>
+      <c r="B785" s="24"/>
     </row>
     <row r="786">
-      <c r="B786" s="29"/>
+      <c r="B786" s="24"/>
     </row>
     <row r="787">
-      <c r="B787" s="29"/>
+      <c r="B787" s="24"/>
     </row>
     <row r="788">
-      <c r="B788" s="29"/>
+      <c r="B788" s="24"/>
     </row>
     <row r="789">
-      <c r="B789" s="29"/>
+      <c r="B789" s="24"/>
     </row>
     <row r="790">
-      <c r="B790" s="29"/>
+      <c r="B790" s="24"/>
     </row>
     <row r="791">
-      <c r="B791" s="29"/>
+      <c r="B791" s="24"/>
     </row>
     <row r="792">
-      <c r="B792" s="29"/>
+      <c r="B792" s="24"/>
     </row>
     <row r="793">
-      <c r="B793" s="29"/>
+      <c r="B793" s="24"/>
     </row>
     <row r="794">
-      <c r="B794" s="29"/>
+      <c r="B794" s="24"/>
     </row>
     <row r="795">
-      <c r="B795" s="29"/>
+      <c r="B795" s="24"/>
     </row>
     <row r="796">
-      <c r="B796" s="29"/>
+      <c r="B796" s="24"/>
     </row>
     <row r="797">
-      <c r="B797" s="29"/>
+      <c r="B797" s="24"/>
     </row>
     <row r="798">
-      <c r="B798" s="29"/>
+      <c r="B798" s="24"/>
     </row>
     <row r="799">
-      <c r="B799" s="29"/>
+      <c r="B799" s="24"/>
     </row>
     <row r="800">
-      <c r="B800" s="29"/>
+      <c r="B800" s="24"/>
     </row>
     <row r="801">
-      <c r="B801" s="29"/>
+      <c r="B801" s="24"/>
     </row>
     <row r="802">
-      <c r="B802" s="29"/>
+      <c r="B802" s="24"/>
     </row>
     <row r="803">
-      <c r="B803" s="29"/>
+      <c r="B803" s="24"/>
     </row>
     <row r="804">
-      <c r="B804" s="29"/>
+      <c r="B804" s="24"/>
     </row>
     <row r="805">
-      <c r="B805" s="29"/>
+      <c r="B805" s="24"/>
     </row>
     <row r="806">
-      <c r="B806" s="29"/>
+      <c r="B806" s="24"/>
     </row>
     <row r="807">
-      <c r="B807" s="29"/>
+      <c r="B807" s="24"/>
     </row>
     <row r="808">
-      <c r="B808" s="29"/>
+      <c r="B808" s="24"/>
     </row>
     <row r="809">
-      <c r="B809" s="29"/>
+      <c r="B809" s="24"/>
     </row>
     <row r="810">
-      <c r="B810" s="29"/>
+      <c r="B810" s="24"/>
     </row>
     <row r="811">
-      <c r="B811" s="29"/>
+      <c r="B811" s="24"/>
     </row>
     <row r="812">
-      <c r="B812" s="29"/>
+      <c r="B812" s="24"/>
     </row>
     <row r="813">
-      <c r="B813" s="29"/>
+      <c r="B813" s="24"/>
     </row>
     <row r="814">
-      <c r="B814" s="29"/>
+      <c r="B814" s="24"/>
     </row>
     <row r="815">
-      <c r="B815" s="29"/>
+      <c r="B815" s="24"/>
     </row>
     <row r="816">
-      <c r="B816" s="29"/>
+      <c r="B816" s="24"/>
     </row>
     <row r="817">
-      <c r="B817" s="29"/>
+      <c r="B817" s="24"/>
     </row>
     <row r="818">
-      <c r="B818" s="29"/>
+      <c r="B818" s="24"/>
     </row>
     <row r="819">
-      <c r="B819" s="29"/>
+      <c r="B819" s="24"/>
     </row>
     <row r="820">
-      <c r="B820" s="29"/>
+      <c r="B820" s="24"/>
     </row>
     <row r="821">
-      <c r="B821" s="29"/>
+      <c r="B821" s="24"/>
     </row>
     <row r="822">
-      <c r="B822" s="29"/>
+      <c r="B822" s="24"/>
     </row>
     <row r="823">
-      <c r="B823" s="29"/>
+      <c r="B823" s="24"/>
     </row>
     <row r="824">
-      <c r="B824" s="29"/>
+      <c r="B824" s="24"/>
     </row>
     <row r="825">
-      <c r="B825" s="29"/>
+      <c r="B825" s="24"/>
     </row>
     <row r="826">
-      <c r="B826" s="29"/>
+      <c r="B826" s="24"/>
     </row>
     <row r="827">
-      <c r="B827" s="29"/>
+      <c r="B827" s="24"/>
     </row>
     <row r="828">
-      <c r="B828" s="29"/>
+      <c r="B828" s="24"/>
     </row>
     <row r="829">
-      <c r="B829" s="29"/>
+      <c r="B829" s="24"/>
     </row>
     <row r="830">
-      <c r="B830" s="29"/>
+      <c r="B830" s="24"/>
     </row>
     <row r="831">
-      <c r="B831" s="29"/>
+      <c r="B831" s="24"/>
     </row>
     <row r="832">
-      <c r="B832" s="29"/>
+      <c r="B832" s="24"/>
     </row>
     <row r="833">
-      <c r="B833" s="29"/>
+      <c r="B833" s="24"/>
     </row>
     <row r="834">
-      <c r="B834" s="29"/>
+      <c r="B834" s="24"/>
     </row>
     <row r="835">
-      <c r="B835" s="29"/>
+      <c r="B835" s="24"/>
     </row>
     <row r="836">
-      <c r="B836" s="29"/>
+      <c r="B836" s="24"/>
     </row>
     <row r="837">
-      <c r="B837" s="29"/>
+      <c r="B837" s="24"/>
     </row>
     <row r="838">
-      <c r="B838" s="29"/>
+      <c r="B838" s="24"/>
     </row>
     <row r="839">
-      <c r="B839" s="29"/>
+      <c r="B839" s="24"/>
     </row>
     <row r="840">
-      <c r="B840" s="29"/>
+      <c r="B840" s="24"/>
     </row>
     <row r="841">
-      <c r="B841" s="29"/>
+      <c r="B841" s="24"/>
     </row>
     <row r="842">
-      <c r="B842" s="29"/>
+      <c r="B842" s="24"/>
     </row>
     <row r="843">
-      <c r="B843" s="29"/>
+      <c r="B843" s="24"/>
     </row>
     <row r="844">
-      <c r="B844" s="29"/>
+      <c r="B844" s="24"/>
     </row>
     <row r="845">
-      <c r="B845" s="29"/>
+      <c r="B845" s="24"/>
     </row>
     <row r="846">
-      <c r="B846" s="29"/>
+      <c r="B846" s="24"/>
     </row>
     <row r="847">
-      <c r="B847" s="29"/>
+      <c r="B847" s="24"/>
     </row>
     <row r="848">
-      <c r="B848" s="29"/>
+      <c r="B848" s="24"/>
     </row>
     <row r="849">
-      <c r="B849" s="29"/>
+      <c r="B849" s="24"/>
     </row>
     <row r="850">
-      <c r="B850" s="29"/>
+      <c r="B850" s="24"/>
     </row>
     <row r="851">
-      <c r="B851" s="29"/>
+      <c r="B851" s="24"/>
     </row>
     <row r="852">
-      <c r="B852" s="29"/>
+      <c r="B852" s="24"/>
     </row>
     <row r="853">
-      <c r="B853" s="29"/>
+      <c r="B853" s="24"/>
     </row>
     <row r="854">
-      <c r="B854" s="29"/>
+      <c r="B854" s="24"/>
     </row>
     <row r="855">
-      <c r="B855" s="29"/>
+      <c r="B855" s="24"/>
     </row>
     <row r="856">
-      <c r="B856" s="29"/>
+      <c r="B856" s="24"/>
     </row>
     <row r="857">
-      <c r="B857" s="29"/>
+      <c r="B857" s="24"/>
     </row>
     <row r="858">
-      <c r="B858" s="29"/>
+      <c r="B858" s="24"/>
     </row>
     <row r="859">
-      <c r="B859" s="29"/>
+      <c r="B859" s="24"/>
     </row>
     <row r="860">
-      <c r="B860" s="29"/>
+      <c r="B860" s="24"/>
     </row>
     <row r="861">
-      <c r="B861" s="29"/>
+      <c r="B861" s="24"/>
     </row>
     <row r="862">
-      <c r="B862" s="29"/>
+      <c r="B862" s="24"/>
     </row>
     <row r="863">
-      <c r="B863" s="29"/>
+      <c r="B863" s="24"/>
     </row>
     <row r="864">
-      <c r="B864" s="29"/>
+      <c r="B864" s="24"/>
     </row>
     <row r="865">
-      <c r="B865" s="29"/>
+      <c r="B865" s="24"/>
     </row>
     <row r="866">
-      <c r="B866" s="29"/>
+      <c r="B866" s="24"/>
     </row>
     <row r="867">
-      <c r="B867" s="29"/>
+      <c r="B867" s="24"/>
     </row>
     <row r="868">
-      <c r="B868" s="29"/>
+      <c r="B868" s="24"/>
     </row>
     <row r="869">
-      <c r="B869" s="29"/>
+      <c r="B869" s="24"/>
     </row>
     <row r="870">
-      <c r="B870" s="29"/>
+      <c r="B870" s="24"/>
     </row>
     <row r="871">
-      <c r="B871" s="29"/>
+      <c r="B871" s="24"/>
     </row>
     <row r="872">
-      <c r="B872" s="29"/>
+      <c r="B872" s="24"/>
     </row>
     <row r="873">
-      <c r="B873" s="29"/>
+      <c r="B873" s="24"/>
     </row>
     <row r="874">
-      <c r="B874" s="29"/>
+      <c r="B874" s="24"/>
     </row>
     <row r="875">
-      <c r="B875" s="29"/>
+      <c r="B875" s="24"/>
     </row>
     <row r="876">
-      <c r="B876" s="29"/>
+      <c r="B876" s="24"/>
     </row>
     <row r="877">
-      <c r="B877" s="29"/>
+      <c r="B877" s="24"/>
     </row>
     <row r="878">
-      <c r="B878" s="29"/>
+      <c r="B878" s="24"/>
     </row>
     <row r="879">
-      <c r="B879" s="29"/>
+      <c r="B879" s="24"/>
     </row>
     <row r="880">
-      <c r="B880" s="29"/>
+      <c r="B880" s="24"/>
     </row>
     <row r="881">
-      <c r="B881" s="29"/>
+      <c r="B881" s="24"/>
     </row>
     <row r="882">
-      <c r="B882" s="29"/>
+      <c r="B882" s="24"/>
     </row>
     <row r="883">
-      <c r="B883" s="29"/>
+      <c r="B883" s="24"/>
     </row>
     <row r="884">
-      <c r="B884" s="29"/>
+      <c r="B884" s="24"/>
     </row>
     <row r="885">
-      <c r="B885" s="29"/>
+      <c r="B885" s="24"/>
     </row>
     <row r="886">
-      <c r="B886" s="29"/>
+      <c r="B886" s="24"/>
     </row>
     <row r="887">
-      <c r="B887" s="29"/>
+      <c r="B887" s="24"/>
     </row>
     <row r="888">
-      <c r="B888" s="29"/>
+      <c r="B888" s="24"/>
     </row>
     <row r="889">
-      <c r="B889" s="29"/>
+      <c r="B889" s="24"/>
     </row>
     <row r="890">
-      <c r="B890" s="29"/>
+      <c r="B890" s="24"/>
     </row>
     <row r="891">
-      <c r="B891" s="29"/>
+      <c r="B891" s="24"/>
     </row>
     <row r="892">
-      <c r="B892" s="29"/>
+      <c r="B892" s="24"/>
     </row>
     <row r="893">
-      <c r="B893" s="29"/>
+      <c r="B893" s="24"/>
     </row>
     <row r="894">
-      <c r="B894" s="29"/>
+      <c r="B894" s="24"/>
     </row>
     <row r="895">
-      <c r="B895" s="29"/>
+      <c r="B895" s="24"/>
     </row>
     <row r="896">
-      <c r="B896" s="29"/>
+      <c r="B896" s="24"/>
     </row>
     <row r="897">
-      <c r="B897" s="29"/>
+      <c r="B897" s="24"/>
     </row>
     <row r="898">
-      <c r="B898" s="29"/>
+      <c r="B898" s="24"/>
     </row>
     <row r="899">
-      <c r="B899" s="29"/>
+      <c r="B899" s="24"/>
     </row>
     <row r="900">
-      <c r="B900" s="29"/>
+      <c r="B900" s="24"/>
     </row>
     <row r="901">
-      <c r="B901" s="29"/>
+      <c r="B901" s="24"/>
     </row>
     <row r="902">
-      <c r="B902" s="29"/>
+      <c r="B902" s="24"/>
     </row>
     <row r="903">
-      <c r="B903" s="29"/>
+      <c r="B903" s="24"/>
     </row>
     <row r="904">
-      <c r="B904" s="29"/>
+      <c r="B904" s="24"/>
     </row>
     <row r="905">
-      <c r="B905" s="29"/>
+      <c r="B905" s="24"/>
     </row>
     <row r="906">
-      <c r="B906" s="29"/>
+      <c r="B906" s="24"/>
     </row>
     <row r="907">
-      <c r="B907" s="29"/>
+      <c r="B907" s="24"/>
     </row>
     <row r="908">
-      <c r="B908" s="29"/>
+      <c r="B908" s="24"/>
     </row>
     <row r="909">
-      <c r="B909" s="29"/>
+      <c r="B909" s="24"/>
     </row>
     <row r="910">
-      <c r="B910" s="29"/>
+      <c r="B910" s="24"/>
     </row>
     <row r="911">
-      <c r="B911" s="29"/>
+      <c r="B911" s="24"/>
     </row>
     <row r="912">
-      <c r="B912" s="29"/>
+      <c r="B912" s="24"/>
     </row>
     <row r="913">
-      <c r="B913" s="29"/>
+      <c r="B913" s="24"/>
     </row>
     <row r="914">
-      <c r="B914" s="29"/>
+      <c r="B914" s="24"/>
     </row>
     <row r="915">
-      <c r="B915" s="29"/>
+      <c r="B915" s="24"/>
     </row>
     <row r="916">
-      <c r="B916" s="29"/>
+      <c r="B916" s="24"/>
     </row>
     <row r="917">
-      <c r="B917" s="29"/>
+      <c r="B917" s="24"/>
     </row>
     <row r="918">
-      <c r="B918" s="29"/>
+      <c r="B918" s="24"/>
     </row>
     <row r="919">
-      <c r="B919" s="29"/>
+      <c r="B919" s="24"/>
     </row>
     <row r="920">
-      <c r="B920" s="29"/>
+      <c r="B920" s="24"/>
     </row>
     <row r="921">
-      <c r="B921" s="29"/>
+      <c r="B921" s="24"/>
     </row>
     <row r="922">
-      <c r="B922" s="29"/>
+      <c r="B922" s="24"/>
     </row>
     <row r="923">
-      <c r="B923" s="29"/>
+      <c r="B923" s="24"/>
     </row>
     <row r="924">
-      <c r="B924" s="29"/>
+      <c r="B924" s="24"/>
     </row>
     <row r="925">
-      <c r="B925" s="29"/>
+      <c r="B925" s="24"/>
     </row>
     <row r="926">
-      <c r="B926" s="29"/>
+      <c r="B926" s="24"/>
     </row>
     <row r="927">
-      <c r="B927" s="29"/>
+      <c r="B927" s="24"/>
     </row>
     <row r="928">
-      <c r="B928" s="29"/>
+      <c r="B928" s="24"/>
     </row>
     <row r="929">
-      <c r="B929" s="29"/>
+      <c r="B929" s="24"/>
     </row>
     <row r="930">
-      <c r="B930" s="29"/>
+      <c r="B930" s="24"/>
     </row>
     <row r="931">
-      <c r="B931" s="29"/>
+      <c r="B931" s="24"/>
     </row>
     <row r="932">
-      <c r="B932" s="29"/>
+      <c r="B932" s="24"/>
     </row>
     <row r="933">
-      <c r="B933" s="29"/>
+      <c r="B933" s="24"/>
     </row>
     <row r="934">
-      <c r="B934" s="29"/>
+      <c r="B934" s="24"/>
     </row>
     <row r="935">
-      <c r="B935" s="29"/>
+      <c r="B935" s="24"/>
     </row>
     <row r="936">
-      <c r="B936" s="29"/>
+      <c r="B936" s="24"/>
     </row>
     <row r="937">
-      <c r="B937" s="29"/>
+      <c r="B937" s="24"/>
     </row>
     <row r="938">
-      <c r="B938" s="29"/>
+      <c r="B938" s="24"/>
     </row>
     <row r="939">
-      <c r="B939" s="29"/>
+      <c r="B939" s="24"/>
     </row>
     <row r="940">
-      <c r="B940" s="29"/>
+      <c r="B940" s="24"/>
     </row>
     <row r="941">
-      <c r="B941" s="29"/>
+      <c r="B941" s="24"/>
     </row>
     <row r="942">
-      <c r="B942" s="29"/>
+      <c r="B942" s="24"/>
     </row>
     <row r="943">
-      <c r="B943" s="29"/>
+      <c r="B943" s="24"/>
     </row>
     <row r="944">
-      <c r="B944" s="29"/>
+      <c r="B944" s="24"/>
     </row>
     <row r="945">
-      <c r="B945" s="29"/>
+      <c r="B945" s="24"/>
     </row>
     <row r="946">
-      <c r="B946" s="29"/>
+      <c r="B946" s="24"/>
     </row>
     <row r="947">
-      <c r="B947" s="29"/>
+      <c r="B947" s="24"/>
     </row>
     <row r="948">
-      <c r="B948" s="29"/>
+      <c r="B948" s="24"/>
     </row>
     <row r="949">
-      <c r="B949" s="29"/>
+      <c r="B949" s="24"/>
     </row>
     <row r="950">
-      <c r="B950" s="29"/>
+      <c r="B950" s="24"/>
     </row>
     <row r="951">
-      <c r="B951" s="29"/>
+      <c r="B951" s="24"/>
     </row>
     <row r="952">
-      <c r="B952" s="29"/>
+      <c r="B952" s="24"/>
     </row>
     <row r="953">
-      <c r="B953" s="29"/>
+      <c r="B953" s="24"/>
     </row>
     <row r="954">
-      <c r="B954" s="29"/>
+      <c r="B954" s="24"/>
     </row>
     <row r="955">
-      <c r="B955" s="29"/>
+      <c r="B955" s="24"/>
     </row>
     <row r="956">
-      <c r="B956" s="29"/>
+      <c r="B956" s="24"/>
     </row>
     <row r="957">
-      <c r="B957" s="29"/>
+      <c r="B957" s="24"/>
     </row>
     <row r="958">
-      <c r="B958" s="29"/>
+      <c r="B958" s="24"/>
     </row>
     <row r="959">
-      <c r="B959" s="29"/>
+      <c r="B959" s="24"/>
     </row>
     <row r="960">
-      <c r="B960" s="29"/>
+      <c r="B960" s="24"/>
     </row>
     <row r="961">
-      <c r="B961" s="29"/>
+      <c r="B961" s="24"/>
     </row>
     <row r="962">
-      <c r="B962" s="29"/>
+      <c r="B962" s="24"/>
     </row>
     <row r="963">
-      <c r="B963" s="29"/>
+      <c r="B963" s="24"/>
     </row>
     <row r="964">
-      <c r="B964" s="29"/>
+      <c r="B964" s="24"/>
     </row>
     <row r="965">
-      <c r="B965" s="29"/>
+      <c r="B965" s="24"/>
     </row>
     <row r="966">
-      <c r="B966" s="29"/>
+      <c r="B966" s="24"/>
     </row>
     <row r="967">
-      <c r="B967" s="29"/>
+      <c r="B967" s="24"/>
     </row>
     <row r="968">
-      <c r="B968" s="29"/>
+      <c r="B968" s="24"/>
     </row>
     <row r="969">
-      <c r="B969" s="29"/>
+      <c r="B969" s="24"/>
     </row>
     <row r="970">
-      <c r="B970" s="29"/>
+      <c r="B970" s="24"/>
     </row>
     <row r="971">
-      <c r="B971" s="29"/>
+      <c r="B971" s="24"/>
     </row>
     <row r="972">
-      <c r="B972" s="29"/>
+      <c r="B972" s="24"/>
     </row>
     <row r="973">
-      <c r="B973" s="29"/>
+      <c r="B973" s="24"/>
     </row>
     <row r="974">
-      <c r="B974" s="29"/>
+      <c r="B974" s="24"/>
     </row>
     <row r="975">
-      <c r="B975" s="29"/>
+      <c r="B975" s="24"/>
     </row>
     <row r="976">
-      <c r="B976" s="29"/>
+      <c r="B976" s="24"/>
     </row>
     <row r="977">
-      <c r="B977" s="29"/>
+      <c r="B977" s="24"/>
     </row>
     <row r="978">
-      <c r="B978" s="29"/>
+      <c r="B978" s="24"/>
     </row>
     <row r="979">
-      <c r="B979" s="29"/>
+      <c r="B979" s="24"/>
     </row>
     <row r="980">
-      <c r="B980" s="29"/>
+      <c r="B980" s="24"/>
     </row>
     <row r="981">
-      <c r="B981" s="29"/>
+      <c r="B981" s="24"/>
     </row>
     <row r="982">
-      <c r="B982" s="29"/>
+      <c r="B982" s="24"/>
     </row>
     <row r="983">
-      <c r="B983" s="29"/>
+      <c r="B983" s="24"/>
     </row>
     <row r="984">
-      <c r="B984" s="29"/>
+      <c r="B984" s="24"/>
     </row>
     <row r="985">
-      <c r="B985" s="29"/>
+      <c r="B985" s="24"/>
     </row>
     <row r="986">
-      <c r="B986" s="29"/>
+      <c r="B986" s="24"/>
     </row>
     <row r="987">
-      <c r="B987" s="29"/>
+      <c r="B987" s="24"/>
     </row>
     <row r="988">
-      <c r="B988" s="29"/>
+      <c r="B988" s="24"/>
     </row>
     <row r="989">
-      <c r="B989" s="29"/>
+      <c r="B989" s="24"/>
     </row>
     <row r="990">
-      <c r="B990" s="29"/>
+      <c r="B990" s="24"/>
     </row>
     <row r="991">
-      <c r="B991" s="29"/>
+      <c r="B991" s="24"/>
     </row>
     <row r="992">
-      <c r="B992" s="29"/>
+      <c r="B992" s="24"/>
     </row>
     <row r="993">
-      <c r="B993" s="29"/>
+      <c r="B993" s="24"/>
     </row>
     <row r="994">
-      <c r="B994" s="29"/>
+      <c r="B994" s="24"/>
     </row>
     <row r="995">
-      <c r="B995" s="29"/>
+      <c r="B995" s="24"/>
     </row>
     <row r="996">
-      <c r="B996" s="29"/>
+      <c r="B996" s="24"/>
     </row>
     <row r="997">
-      <c r="B997" s="29"/>
+      <c r="B997" s="24"/>
     </row>
     <row r="998">
-      <c r="B998" s="29"/>
+      <c r="B998" s="24"/>
     </row>
     <row r="999">
-      <c r="B999" s="29"/>
+      <c r="B999" s="24"/>
     </row>
     <row r="1000">
-      <c r="B1000" s="29"/>
+      <c r="B1000" s="24"/>
     </row>
     <row r="1001">
-      <c r="B1001" s="29"/>
+      <c r="B1001" s="24"/>
     </row>
     <row r="1002">
-      <c r="B1002" s="29"/>
+      <c r="B1002" s="24"/>
     </row>
     <row r="1003">
-      <c r="B1003" s="29"/>
+      <c r="B1003" s="24"/>
     </row>
     <row r="1004">
-      <c r="B1004" s="29"/>
+      <c r="B1004" s="24"/>
     </row>
     <row r="1005">
-      <c r="B1005" s="29"/>
+      <c r="B1005" s="24"/>
     </row>
     <row r="1006">
-      <c r="B1006" s="29"/>
+      <c r="B1006" s="24"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/src/data/Sources_and_Definitions.xlsx
+++ b/src/data/Sources_and_Definitions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="404">
   <si>
     <t>Date of Data Collection</t>
   </si>
@@ -262,6 +262,21 @@
     </r>
   </si>
   <si>
+    <t>Children in Placement (includes all placement types)</t>
+  </si>
+  <si>
+    <t>Children in Non-Relative Foster Care</t>
+  </si>
+  <si>
+    <t>Children in Kinship Care (includes relative and fictive kin)</t>
+  </si>
+  <si>
+    <t>Number of Licensed Providers (Includes Providers Placed on Hold)</t>
+  </si>
+  <si>
+    <t>Children Available for Adoption (Post-TPR)</t>
+  </si>
+  <si>
     <t>Delaware</t>
   </si>
   <si>
@@ -516,7 +531,7 @@
     <t>Number of total open family preservation cases</t>
   </si>
   <si>
-    <t>Mean time elapsed between termination of parental rights and adoption (days)</t>
+    <t>Mean time elapsed between termination of parental rights and adoption (months)</t>
   </si>
   <si>
     <t>Iowa</t>
@@ -821,6 +836,9 @@
     <t>Number of famillies receiving in-home services</t>
   </si>
   <si>
+    <t>The number of children exiting to adoptive homes in CY 2024</t>
+  </si>
+  <si>
     <t>Montana</t>
   </si>
   <si>
@@ -878,6 +896,12 @@
   </si>
   <si>
     <t>The count of children in relative care.</t>
+  </si>
+  <si>
+    <t>The % of children reuniting with caretaker, parent or other relative in SFY 2024.</t>
+  </si>
+  <si>
+    <t>The number of adoptions in SFY 2024.</t>
   </si>
   <si>
     <t>New Hampshire</t>
@@ -2221,101 +2245,116 @@
       <c r="D8" s="14" t="s">
         <v>64</v>
       </c>
+      <c r="E8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B9" s="10">
         <v>45504.0</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B10" s="10">
         <v>45657.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B11" s="10">
         <v>45657.0</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>24</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="N11" s="6" t="s">
         <v>25</v>
@@ -2323,135 +2362,135 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B12" s="10">
         <v>45659.0</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B13" s="10">
         <v>45657.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B14" s="10">
         <v>45657.0</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K14" s="6"/>
       <c r="N14" s="6"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B15" s="10">
         <v>45657.0</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>24</v>
@@ -2462,70 +2501,70 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B16" s="10">
         <v>45657.0</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>24</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="N16" s="6" t="s">
         <v>24</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B17" s="10">
         <v>45757.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>24</v>
@@ -2534,94 +2573,94 @@
         <v>25</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B18" s="10">
         <v>45657.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>24</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B19" s="20">
         <v>45655.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>24</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B20" s="10">
         <v>45769.0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>24</v>
@@ -2632,83 +2671,83 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B21" s="10">
         <v>45658.0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B22" s="10">
         <v>45657.0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B23" s="10">
         <v>45657.0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>24</v>
@@ -2717,39 +2756,39 @@
         <v>25</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B24" s="10">
         <v>45657.0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>24</v>
@@ -2760,125 +2799,125 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B25" s="10">
         <v>45657.0</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B26" s="10">
         <v>45770.0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B27" s="5">
         <v>2024.0</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>25</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B28" s="24"/>
       <c r="C28" s="6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D28" s="14"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B29" s="10">
         <v>45657.0</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>24</v>
@@ -2889,33 +2928,37 @@
     </row>
     <row r="30">
       <c r="A30" s="25" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B30" s="26">
         <v>45657.0</v>
       </c>
       <c r="C30" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>214</v>
-      </c>
       <c r="F30" s="27" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H30" s="28"/>
       <c r="I30" s="25"/>
       <c r="J30" s="28"/>
-      <c r="K30" s="25"/>
+      <c r="K30" s="25" t="s">
+        <v>230</v>
+      </c>
       <c r="L30" s="28"/>
       <c r="M30" s="28"/>
-      <c r="N30" s="25"/>
+      <c r="N30" s="25" t="s">
+        <v>231</v>
+      </c>
       <c r="O30" s="28"/>
       <c r="P30" s="28"/>
       <c r="Q30" s="28"/>
@@ -2925,34 +2968,34 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B31" s="10">
         <v>45657.0</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>24</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>25</v>
@@ -2960,25 +3003,25 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B32" s="10">
         <v>45657.0</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>20</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>24</v>
@@ -2989,92 +3032,92 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B33" s="10">
         <v>45657.0</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E33" s="29" t="s">
         <v>20</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>24</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B34" s="10">
         <v>45763.0</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B35" s="10">
         <v>45658.0</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>22</v>
@@ -3083,558 +3126,558 @@
         <v>24</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B36" s="10">
         <v>45657.0</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="E36" s="30" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B37" s="10">
         <v>45658.0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>24</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B38" s="10">
         <v>45657.0</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>29</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B39" s="10">
         <v>45657.0</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B40" s="10">
         <v>44834.0</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B41" s="10">
         <v>45748.0</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B42" s="10">
         <v>45803.0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B43" s="10">
         <v>45473.0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B44" s="10">
         <v>45657.0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>5</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="O44" s="6"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B45" s="10">
         <v>45535.0</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>24</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="O45" s="6"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D46" s="14"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B47" s="10">
         <v>45565.0</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B48" s="10">
         <v>45658.0</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B49" s="10">
         <v>45473.0</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B50" s="10">
         <v>45657.0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B51" s="10">
         <v>45291.0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B52" s="10">
         <v>45657.0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="53">

--- a/src/data/Sources_and_Definitions.xlsx
+++ b/src/data/Sources_and_Definitions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="406">
   <si>
     <t>Date of Data Collection</t>
   </si>
@@ -460,7 +460,7 @@
     <t>Number of foster children</t>
   </si>
   <si>
-    <t>Number of children placed with a foster family</t>
+    <t>Number of children placed with a foster family, including kinship placements</t>
   </si>
   <si>
     <t>Number of children placed with a relative or fictive kin</t>
@@ -715,7 +715,7 @@
     <t>Number of children in all placement types</t>
   </si>
   <si>
-    <t>Number of children in family-like foster care</t>
+    <t>Number of children in family-like foster care, including kinship care</t>
   </si>
   <si>
     <t>Number of children placed out-of-county</t>
@@ -1388,6 +1388,9 @@
     </r>
   </si>
   <si>
+    <t>Number of children in family-like foster care</t>
+  </si>
+  <si>
     <t>Number of children in relative/kinship placement</t>
   </si>
   <si>
@@ -1431,7 +1434,7 @@
     <t>The number of children with a current placement of relative foster family</t>
   </si>
   <si>
-    <t>The percent of exits to reunification in FY 2024</t>
+    <t>The percent of exits to reunification in CY 2024</t>
   </si>
   <si>
     <t>The number of adoptions in FY 2024</t>
@@ -1490,10 +1493,13 @@
     <t>The number of children in state custody</t>
   </si>
   <si>
-    <t>The number of children in certi</t>
+    <t>The number of children in foster care (including kinship)</t>
   </si>
   <si>
     <t>The number of children in kinship placements (certified and pending)</t>
+  </si>
+  <si>
+    <t>The number of children placed out of state.</t>
   </si>
   <si>
     <t>The total number of CPA and kinship homes</t>
@@ -3511,173 +3517,176 @@
         <v>176</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>183</v>
+        <v>360</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B48" s="10">
         <v>45658.0</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>303</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B49" s="10">
         <v>45473.0</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B50" s="10">
         <v>45657.0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>390</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B51" s="10">
-        <v>45291.0</v>
+        <v>45657.0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>284</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B52" s="10">
         <v>45657.0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>255</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="53">

--- a/src/data/Sources_and_Definitions.xlsx
+++ b/src/data/Sources_and_Definitions.xlsx
@@ -1690,10 +1690,10 @@
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1755,13 +1755,13 @@
     <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
